--- a/Harewood/38_Harewood_Bid_Leveling_Sheet.xlsx
+++ b/Harewood/38_Harewood_Bid_Leveling_Sheet.xlsx
@@ -15,27 +15,27 @@
     <sheet name="Flags &amp; Next Steps" sheetId="5" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" name="BEAM_CAR" vbProcedure="false">'Bid Leveling'!$J$66</definedName>
-    <definedName function="false" hidden="false" name="BEAM_INT" vbProcedure="false">'Bid Leveling'!$F$66</definedName>
-    <definedName function="false" hidden="false" name="EXT_CAR" vbProcedure="false">'Bid Leveling'!$J$36</definedName>
-    <definedName function="false" hidden="false" name="EXT_INT" vbProcedure="false">'Bid Leveling'!$F$36</definedName>
-    <definedName function="false" hidden="false" name="FIN_CAR" vbProcedure="false">'Bid Leveling'!$J$57</definedName>
-    <definedName function="false" hidden="false" name="FIN_INT" vbProcedure="false">'Bid Leveling'!$F$57</definedName>
+    <definedName function="false" hidden="false" name="BEAM_CAR" vbProcedure="false">'Bid Leveling'!$J$70</definedName>
+    <definedName function="false" hidden="false" name="BEAM_INT" vbProcedure="false">'Bid Leveling'!$F$70</definedName>
+    <definedName function="false" hidden="false" name="EXT_CAR" vbProcedure="false">'Bid Leveling'!$J$39</definedName>
+    <definedName function="false" hidden="false" name="EXT_INT" vbProcedure="false">'Bid Leveling'!$F$39</definedName>
+    <definedName function="false" hidden="false" name="FIN_CAR" vbProcedure="false">'Bid Leveling'!$J$60</definedName>
+    <definedName function="false" hidden="false" name="FIN_INT" vbProcedure="false">'Bid Leveling'!$F$60</definedName>
     <definedName function="false" hidden="false" name="FVBUILD" vbProcedure="false">'FV Scope Build-up'!$F$18</definedName>
-    <definedName function="false" hidden="false" name="GEN_CAR" vbProcedure="false">'Bid Leveling'!$J$18</definedName>
-    <definedName function="false" hidden="false" name="GEN_INT" vbProcedure="false">'Bid Leveling'!$F$18</definedName>
-    <definedName function="false" hidden="false" name="GRANDCAR" vbProcedure="false">'Bid Leveling'!$J$68</definedName>
-    <definedName function="false" hidden="false" name="LOWBID_TOTAL" vbProcedure="false">'Bid Leveling'!$W$68</definedName>
+    <definedName function="false" hidden="false" name="GEN_CAR" vbProcedure="false">'Bid Leveling'!$J$21</definedName>
+    <definedName function="false" hidden="false" name="GEN_INT" vbProcedure="false">'Bid Leveling'!$F$21</definedName>
+    <definedName function="false" hidden="false" name="GRANDCAR" vbProcedure="false">'Bid Leveling'!$J$72</definedName>
+    <definedName function="false" hidden="false" name="LOWBID_TOTAL" vbProcedure="false">'Bid Leveling'!$W$72</definedName>
     <definedName function="false" hidden="false" name="MARGIN" vbProcedure="false">Summary!$B$6</definedName>
-    <definedName function="false" hidden="false" name="MECH_CAR" vbProcedure="false">'Bid Leveling'!$J$43</definedName>
-    <definedName function="false" hidden="false" name="MECH_INT" vbProcedure="false">'Bid Leveling'!$F$43</definedName>
-    <definedName function="false" hidden="false" name="PORCH_CAR" vbProcedure="false">'Bid Leveling'!$J$24</definedName>
-    <definedName function="false" hidden="false" name="PORCH_INT" vbProcedure="false">'Bid Leveling'!$F$24</definedName>
-    <definedName function="false" hidden="false" name="STRUCT_CAR" vbProcedure="false">'Bid Leveling'!$J$29</definedName>
-    <definedName function="false" hidden="false" name="STRUCT_INT" vbProcedure="false">'Bid Leveling'!$F$29</definedName>
-    <definedName function="false" hidden="false" name="TIME_INT" vbProcedure="false">'Bid Leveling'!$J$15:$J$17</definedName>
-    <definedName function="false" hidden="false" name="TRADES_CAR" vbProcedure="false">'Bid Leveling'!$J$47</definedName>
-    <definedName function="false" hidden="false" name="TRADES_INT" vbProcedure="false">'Bid Leveling'!$F$47</definedName>
+    <definedName function="false" hidden="false" name="MECH_CAR" vbProcedure="false">'Bid Leveling'!$J$46</definedName>
+    <definedName function="false" hidden="false" name="MECH_INT" vbProcedure="false">'Bid Leveling'!$F$46</definedName>
+    <definedName function="false" hidden="false" name="PORCH_CAR" vbProcedure="false">'Bid Leveling'!$J$27</definedName>
+    <definedName function="false" hidden="false" name="PORCH_INT" vbProcedure="false">'Bid Leveling'!$F$27</definedName>
+    <definedName function="false" hidden="false" name="STRUCT_CAR" vbProcedure="false">'Bid Leveling'!$J$32</definedName>
+    <definedName function="false" hidden="false" name="STRUCT_INT" vbProcedure="false">'Bid Leveling'!$F$32</definedName>
+    <definedName function="false" hidden="false" name="TIME_INT" vbProcedure="false">'Bid Leveling'!$J$18:$J$20</definedName>
+    <definedName function="false" hidden="false" name="TRADES_CAR" vbProcedure="false">'Bid Leveling'!$J$50</definedName>
+    <definedName function="false" hidden="false" name="TRADES_INT" vbProcedure="false">'Bid Leveling'!$F$50</definedName>
     <definedName function="false" hidden="false" name="WEEKS" vbProcedure="false">Summary!$B$7</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="342" uniqueCount="277">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="304">
   <si>
     <t xml:space="preserve">38 Harewood Ave: Bid Leveling Summary</t>
   </si>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">Construction duration (weeks)</t>
   </si>
   <si>
-    <t xml:space="preserve">Per Raff: ~6 months. Drives PM, site labour and overhead lines.</t>
+    <t xml:space="preserve">24 weeks + 3 weeks for occupied-home sequencing (structure first, clients living in). Drives PM, site labour, overhead.</t>
   </si>
   <si>
     <t xml:space="preserve">Option A contract price (pre-HST)</t>
@@ -98,6 +98,12 @@
     <t xml:space="preserve">Ontario HST.</t>
   </si>
   <si>
+    <t xml:space="preserve">PROPOSED revised selling price (pre-HST)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter the price you will put in the revised Joist. Margin checks below update.</t>
+  </si>
+  <si>
     <t xml:space="preserve">COST ROLL-UP (from Bid Leveling tab)</t>
   </si>
   <si>
@@ -212,6 +218,24 @@
     <t xml:space="preserve">Margin column = margin at current price using all low bids.</t>
   </si>
   <si>
+    <t xml:space="preserve">REVISED PROPOSAL price (input B11): net profit, all-in carried cost</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post site-visit scope incl. beam, ceiling at no charge, temp stair, live-in protection, 27 wks.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVISED PROPOSAL: profit using all low bids</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upside if low bids hold.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVISED PROPOSAL: increase vs current quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Margin column = % increase over current Option A + beam.</t>
+  </si>
+  <si>
     <t xml:space="preserve">38 Harewood Ave: Bid Leveling Sheet</t>
   </si>
   <si>
@@ -341,6 +365,24 @@
     <t xml:space="preserve">Allowance.</t>
   </si>
   <si>
+    <t xml:space="preserve">Temporary exterior stair + landing + temp door to 2nd floor (side yard), install &amp; remove</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site visit: clients living in house. Side A (driveway) has A/C condenser + PVC vents: protect.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied-home protection: dust walls, zip doors, floor/stair protection, daily clean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clients stay in; short move-outs during ceiling opening.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto Hydro disconnect/reconnect day coordination + temp power while occupied</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photos: overhead drop lands on side-B gable being raised. Mast in FV $4,500 bid; this covers temp power/coordination.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Final clean, deficiencies, final inspections</t>
   </si>
   <si>
@@ -527,10 +569,10 @@
     <t xml:space="preserve">Existing panel is 100A (S1.01). Not on drawings: confirm client understands it is in scope.</t>
   </si>
   <si>
-    <t xml:space="preserve">Furnace / water heater re-vent (chimney removed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allowance. HWT likely vents in chimney; may need direct-vent replacement (rental?).</t>
+    <t xml:space="preserve">Chimney: cap/reroute plumbing stack at base, HWT vent check (chimney not disturbed below roof)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site visit: chimney taken down to base ~1 yr ago; clients do not want it disturbed. Photos: PVC side-wall vents (HE furnace); HWT vent unclear. Furnace recently replaced (Direct Energy sticker: rental?).</t>
   </si>
   <si>
     <t xml:space="preserve">Attic R60 blown-in + baffles</t>
@@ -620,7 +662,7 @@
     <t xml:space="preserve">Basement footing pads + posts</t>
   </si>
   <si>
-    <t xml:space="preserve">Drawings (A3.01) show posts on solid blocking to foundation wall: likely $0. Keep until site-verified.</t>
+    <t xml:space="preserve">A3.01: posts on solid blocking to foundation wall. Photos: interior block wall in basement (likely bearing line). Reduced to $1,500 allowance until verified.</t>
   </si>
   <si>
     <t xml:space="preserve">Electrical relocation out of wall</t>
@@ -629,7 +671,16 @@
     <t xml:space="preserve">Drywall close-in &amp; beam wrap, Level 4, primed</t>
   </si>
   <si>
-    <t xml:space="preserve">Floor patch at old wall line</t>
+    <t xml:space="preserve">Floor transition at old wall line: match existing, wide transition, or quartz threshold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site visit: main-floor floors stay; transition only. Options to client.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Main-floor plaster ceiling: remove &amp; replace with drywall L4 at beam area (~400 SF), INCLUDED AT NO CHARGE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raff: include at no charge. Clients not attached to plaster. Cost carried, $0 sell line in Joist.</t>
   </si>
   <si>
     <t xml:space="preserve">Engineer review</t>
@@ -851,10 +902,10 @@
     <t xml:space="preserve">CA $3,800 roofing and $3,800 aluminum are well below carried. Confirm scope parity (vents, flashing band) then decide. Potential saving ≈ $6,900.</t>
   </si>
   <si>
-    <t xml:space="preserve">Stair finishing conflict</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sep 4 text: finishing included. Sep 7 email: stair finishing removed. Joist: included. Decide, then align Joist + carried cost.</t>
+    <t xml:space="preserve">Stair capping</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revised Joist: stair capping ($5,000) included per Raff; replaces the Sep 7 'removed' wording.</t>
   </si>
   <si>
     <t xml:space="preserve">Bathroom: shower-only vs tub</t>
@@ -866,19 +917,49 @@
     <t xml:space="preserve">Beam footings</t>
   </si>
   <si>
-    <t xml:space="preserve">A3.01 shows posts on blocking to foundation wall: $3,000 allowance likely drops to $0 once verified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water heater / chimney</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confirm what vents in the chimney; allowance $2,000 may not cover a direct-vent HWT if owned (not rental).</t>
+    <t xml:space="preserve">A3.01 shows posts on blocking to foundation wall; basement photos show interior block wall. Allowance cut to $1,500; $0 once verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chimney / plumbing stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site visit: chimney already down to base ~1 yr ago; clients do not want it disturbed. Raff to check plumbing stack in basement. Confirm HWT vent + rental status (Direct Energy sticker).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water service size</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mark says OK, but new 2nd-floor bath adds fixtures. Not carried. Exclusion in Joist; upgrade by change order ($5-10K if needed).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Porch: coal cellar / unpermitted existing porch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Possible coal cellar under porch; existing porch unpermitted. Not carried. Change-order clause in Joist.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toronto Hydro mast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Overhead drop + conduit on side-B gable being raised. Mast relocation in FV bid ($4,500); outage day coordination now carried ($600).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plaster ceiling at no charge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carried at cost ($3,500, ~400 SF L4 drywall); shown as $0 line in Joist as a goodwill item. Confirm FV prices it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Occupied home</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clients stay in. Temp exterior stair ($3,800), live-in protection ($3,000) and +3 weeks (27 total) now carried.</t>
   </si>
   <si>
     <t xml:space="preserve">Pricing vs 40% target</t>
   </si>
   <si>
-    <t xml:space="preserve">See Summary: current price is far below a 40% margin once PM, labour and overhead are included. Decide the margin basis before re-issuing the Joist.</t>
+    <t xml:space="preserve">See Summary rows 38-40: revised proposal price (B11) vs all-in carried cost. Set B11 to the number going into the revised Joist.</t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1589,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:D37"/>
+  <dimension ref="A1:D40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="58"/>
@@ -1559,12 +1640,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="9" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="8" t="s">
@@ -1607,9 +1688,21 @@
         <v>15</v>
       </c>
     </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" s="10" t="n">
+        <v>339000</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="8" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
@@ -1617,35 +1710,35 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B14" s="11" t="n">
         <f aca="false">GEN_INT</f>
-        <v>100700</v>
+        <v>118000</v>
       </c>
       <c r="C14" s="11" t="n">
         <f aca="false">GEN_CAR</f>
-        <v>100700</v>
+        <v>118000</v>
       </c>
       <c r="D14" s="6"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B15" s="11" t="n">
         <f aca="false">PORCH_INT</f>
@@ -1659,7 +1752,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B16" s="11" t="n">
         <f aca="false">STRUCT_INT</f>
@@ -1673,7 +1766,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B17" s="11" t="n">
         <f aca="false">EXT_INT</f>
@@ -1687,7 +1780,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="6" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B18" s="11" t="n">
         <f aca="false">MECH_INT</f>
@@ -1701,7 +1794,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="6" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B19" s="11" t="n">
         <f aca="false">TRADES_INT</f>
@@ -1715,7 +1808,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B20" s="11" t="n">
         <f aca="false">FIN_INT</f>
@@ -1729,65 +1822,65 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B21" s="11" t="n">
         <f aca="false">BEAM_INT</f>
-        <v>8200</v>
+        <v>10200</v>
       </c>
       <c r="C21" s="11" t="n">
         <f aca="false">BEAM_CAR</f>
-        <v>8200</v>
+        <v>10200</v>
       </c>
       <c r="D21" s="6"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B22" s="13" t="n">
         <f aca="false">SUM(B14:B21)</f>
-        <v>289498.9</v>
+        <v>308798.9</v>
       </c>
       <c r="C22" s="13" t="n">
         <f aca="false">SUM(C14:C21)</f>
-        <v>272393.01</v>
+        <v>291693.01</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B23" s="11" t="n">
         <f aca="false">SUM(TIME_INT)</f>
-        <v>79200</v>
+        <v>89100</v>
       </c>
       <c r="C23" s="11" t="n">
         <f aca="false">SUM(TIME_INT)</f>
-        <v>79200</v>
+        <v>89100</v>
       </c>
       <c r="D23" s="6"/>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B24" s="14" t="n">
         <f aca="false">B22-B23</f>
-        <v>210298.9</v>
+        <v>219698.9</v>
       </c>
       <c r="C24" s="14" t="n">
         <f aca="false">C22-C23</f>
-        <v>193193.01</v>
+        <v>202593.01</v>
       </c>
       <c r="D24" s="6"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1795,21 +1888,21 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B28" s="14" t="n">
         <f aca="false">B8+B9</f>
@@ -1817,138 +1910,186 @@
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B29" s="14" t="n">
         <f aca="false">B28-C22</f>
-        <v>15486.74</v>
+        <v>-3813.26000000001</v>
       </c>
       <c r="C29" s="16" t="n">
         <f aca="false">IF(B28=0,0,B29/B28)</f>
-        <v>0.0537958644190847</v>
+        <v>-0.0132460167830492</v>
       </c>
       <c r="D29" s="8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="13" t="n">
         <f aca="false">C22/(1-B6)</f>
-        <v>453988.35</v>
+        <v>486155.016666667</v>
       </c>
       <c r="C30" s="17" t="n">
         <f aca="false">B6</f>
         <v>0.4</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B31" s="14" t="n">
         <f aca="false">B30-B28</f>
-        <v>166108.6</v>
+        <v>198275.266666667</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="8" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B32" s="13" t="n">
         <f aca="false">C22*(1+B6)</f>
-        <v>381350.214</v>
+        <v>408370.214</v>
       </c>
       <c r="C32" s="17" t="n">
         <f aca="false">IF(B32=0,0,(B32-C22)/B32)</f>
         <v>0.285714285714286</v>
       </c>
       <c r="D32" s="8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="6" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B33" s="14" t="n">
         <f aca="false">B32-B28</f>
-        <v>93470.464</v>
+        <v>120490.464</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="8"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B34" s="13" t="n">
         <f aca="false">C24/(1-B6)</f>
-        <v>321988.35</v>
+        <v>337655.016666667</v>
       </c>
       <c r="C34" s="17" t="n">
         <f aca="false">B6</f>
         <v>0.4</v>
       </c>
       <c r="D34" s="8" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="6" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B35" s="14" t="n">
         <f aca="false">B34-B28</f>
-        <v>34108.6</v>
+        <v>49775.2666666667</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="8"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B36" s="14" t="n">
         <f aca="false">B34-C22</f>
-        <v>49595.34</v>
+        <v>45962.0066666667</v>
       </c>
       <c r="C36" s="16" t="n">
         <f aca="false">IF(B34=0,0,B36/B34)</f>
-        <v>0.154028367796537</v>
+        <v>0.136121201812442</v>
       </c>
       <c r="D36" s="8" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B37" s="14" t="n">
         <f aca="false">LOWBID_TOTAL</f>
-        <v>263612.35</v>
+        <v>282912.35</v>
       </c>
       <c r="C37" s="16" t="n">
         <f aca="false">IF(B28=0,0,(B28-B37)/B28)</f>
-        <v>0.0842970024810707</v>
+        <v>0.0172551212789369</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>53</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="B38" s="13" t="n">
+        <f aca="false">B11-C22</f>
+        <v>47306.99</v>
+      </c>
+      <c r="C38" s="17" t="n">
+        <f aca="false">IF(B11=0,0,B38/B11)</f>
+        <v>0.139548643067847</v>
+      </c>
+      <c r="D38" s="8" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="B39" s="14" t="n">
+        <f aca="false">B11-B37</f>
+        <v>56087.65</v>
+      </c>
+      <c r="C39" s="16" t="n">
+        <f aca="false">IF(B11=0,0,B39/B11)</f>
+        <v>0.165450294985251</v>
+      </c>
+      <c r="D39" s="8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B40" s="14" t="n">
+        <f aca="false">B11-B28</f>
+        <v>51120.25</v>
+      </c>
+      <c r="C40" s="16" t="n">
+        <f aca="false">IF(B28=0,0,B40/B28)</f>
+        <v>0.177575011788776</v>
+      </c>
+      <c r="D40" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -1962,18 +2103,28 @@
       <formula>0.15</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="C38">
+    <cfRule type="cellIs" priority="4" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C39">
+    <cfRule type="cellIs" priority="5" operator="lessThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>0.15</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="B31">
-    <cfRule type="cellIs" priority="4" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B33">
-    <cfRule type="cellIs" priority="5" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="7" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B35">
-    <cfRule type="cellIs" priority="6" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="cellIs" priority="8" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1992,7 +2143,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:X68"/>
+  <dimension ref="A1:X72"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2022,17 +2173,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="18" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -2058,82 +2209,82 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="19" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C5" s="19" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="G5" s="19" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H5" s="19" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="I5" s="19" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="J5" s="19" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="K5" s="19" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="L5" s="19" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="M5" s="19" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="N5" s="19" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="O5" s="19" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="P5" s="19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="Q5" s="19" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="R5" s="19" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="S5" s="19" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="T5" s="19" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="U5" s="19" t="s">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="V5" s="19" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="W5" s="5" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="X5" s="5" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="20"/>
       <c r="B6" s="21" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="C6" s="20"/>
       <c r="D6" s="20"/>
@@ -2161,7 +2312,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>3000</v>
@@ -2170,7 +2321,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">C7*D7</f>
@@ -2178,7 +2329,7 @@
       </c>
       <c r="G7" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J7/GRANDCAR)</f>
-        <v>0.0110134984741349</v>
+        <v>0.0102847853639002</v>
       </c>
       <c r="H7" s="14" t="n">
         <f aca="false">J7/(1-MARGIN)</f>
@@ -2210,7 +2361,7 @@
       <c r="T7" s="6"/>
       <c r="U7" s="27"/>
       <c r="V7" s="8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="W7" s="14" t="n">
         <f aca="false">IF(M7="",F7,M7)</f>
@@ -2226,7 +2377,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>3500</v>
@@ -2235,7 +2386,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">C8*D8</f>
@@ -2243,7 +2394,7 @@
       </c>
       <c r="G8" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J8/GRANDCAR)</f>
-        <v>0.0128490815531573</v>
+        <v>0.0119989162578836</v>
       </c>
       <c r="H8" s="14" t="n">
         <f aca="false">J8/(1-MARGIN)</f>
@@ -2275,7 +2426,7 @@
       <c r="T8" s="6"/>
       <c r="U8" s="27"/>
       <c r="V8" s="8" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="W8" s="14" t="n">
         <f aca="false">IF(M8="",F8,M8)</f>
@@ -2291,7 +2442,7 @@
         <v>3</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>2000</v>
@@ -2300,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">C9*D9</f>
@@ -2308,7 +2459,7 @@
       </c>
       <c r="G9" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J9/GRANDCAR)</f>
-        <v>0.0073423323160899</v>
+        <v>0.00685652357593348</v>
       </c>
       <c r="H9" s="14" t="n">
         <f aca="false">J9/(1-MARGIN)</f>
@@ -2340,7 +2491,7 @@
       <c r="T9" s="6"/>
       <c r="U9" s="27"/>
       <c r="V9" s="8" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="W9" s="14" t="n">
         <f aca="false">IF(M9="",F9,M9)</f>
@@ -2356,7 +2507,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>2500</v>
@@ -2365,7 +2516,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">C10*D10</f>
@@ -2373,7 +2524,7 @@
       </c>
       <c r="G10" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J10/GRANDCAR)</f>
-        <v>0.00917791539511238</v>
+        <v>0.00857065446991685</v>
       </c>
       <c r="H10" s="14" t="n">
         <f aca="false">J10/(1-MARGIN)</f>
@@ -2405,7 +2556,7 @@
       <c r="T10" s="6"/>
       <c r="U10" s="27"/>
       <c r="V10" s="8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="W10" s="14" t="n">
         <f aca="false">IF(M10="",F10,M10)</f>
@@ -2421,7 +2572,7 @@
         <v>5</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>1500</v>
@@ -2430,7 +2581,7 @@
         <v>2</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">C11*D11</f>
@@ -2438,7 +2589,7 @@
       </c>
       <c r="G11" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J11/GRANDCAR)</f>
-        <v>0.0110134984741349</v>
+        <v>0.0102847853639002</v>
       </c>
       <c r="H11" s="14" t="n">
         <f aca="false">J11/(1-MARGIN)</f>
@@ -2470,7 +2621,7 @@
       <c r="T11" s="6"/>
       <c r="U11" s="27"/>
       <c r="V11" s="8" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="W11" s="14" t="n">
         <f aca="false">IF(M11="",F11,M11)</f>
@@ -2486,7 +2637,7 @@
         <v>6</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="C12" s="10" t="n">
         <v>1500</v>
@@ -2495,7 +2646,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F12" s="14" t="n">
         <f aca="false">C12*D12</f>
@@ -2503,7 +2654,7 @@
       </c>
       <c r="G12" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J12/GRANDCAR)</f>
-        <v>0.00550674923706743</v>
+        <v>0.00514239268195011</v>
       </c>
       <c r="H12" s="14" t="n">
         <f aca="false">J12/(1-MARGIN)</f>
@@ -2535,7 +2686,7 @@
       <c r="T12" s="6"/>
       <c r="U12" s="27"/>
       <c r="V12" s="8" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="W12" s="14" t="n">
         <f aca="false">IF(M12="",F12,M12)</f>
@@ -2551,7 +2702,7 @@
         <v>7</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C13" s="10" t="n">
         <v>1500</v>
@@ -2560,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">C13*D13</f>
@@ -2568,7 +2719,7 @@
       </c>
       <c r="G13" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J13/GRANDCAR)</f>
-        <v>0.00550674923706743</v>
+        <v>0.00514239268195011</v>
       </c>
       <c r="H13" s="14" t="n">
         <f aca="false">J13/(1-MARGIN)</f>
@@ -2600,7 +2751,7 @@
       <c r="T13" s="6"/>
       <c r="U13" s="27"/>
       <c r="V13" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="W13" s="14" t="n">
         <f aca="false">IF(M13="",F13,M13)</f>
@@ -2611,41 +2762,41 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="22" t="n">
         <v>8</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">C14*D14</f>
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="G14" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J14/GRANDCAR)</f>
-        <v>0.0165202477112023</v>
+        <v>0.0130273947942736</v>
       </c>
       <c r="H14" s="14" t="n">
         <f aca="false">J14/(1-MARGIN)</f>
-        <v>7500</v>
+        <v>6333.33333333333</v>
       </c>
       <c r="I14" s="14" t="n">
         <f aca="false">H14-J14</f>
-        <v>3000</v>
+        <v>2533.33333333333</v>
       </c>
       <c r="J14" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L14),L14,IF(COUNT(O14,Q14,S14,U14)&gt;0,MIN(O14,Q14,S14,U14),F14))</f>
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="K14" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L14),"Override",IF(COUNT(O14,Q14,S14,U14)&gt;0,"Low bid","Internal rate"))</f>
@@ -2665,11 +2816,11 @@
       <c r="T14" s="6"/>
       <c r="U14" s="27"/>
       <c r="V14" s="8" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="W14" s="14" t="n">
         <f aca="false">IF(M14="",F14,M14)</f>
-        <v>4500</v>
+        <v>3800</v>
       </c>
       <c r="X14" s="14" t="n">
         <f aca="false">J14-F14</f>
@@ -2681,37 +2832,36 @@
         <v>9</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1700</v>
-      </c>
-      <c r="D15" s="28" t="n">
-        <f aca="false">WEEKS</f>
-        <v>24</v>
+        <v>3000</v>
+      </c>
+      <c r="D15" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">C15*D15</f>
-        <v>40800</v>
+        <v>3000</v>
       </c>
       <c r="G15" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J15/GRANDCAR)</f>
-        <v>0.149783579248234</v>
+        <v>0.0102847853639002</v>
       </c>
       <c r="H15" s="14" t="n">
         <f aca="false">J15/(1-MARGIN)</f>
-        <v>68000</v>
+        <v>5000</v>
       </c>
       <c r="I15" s="14" t="n">
         <f aca="false">H15-J15</f>
-        <v>27200</v>
+        <v>2000</v>
       </c>
       <c r="J15" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L15),L15,IF(COUNT(O15,Q15,S15,U15)&gt;0,MIN(O15,Q15,S15,U15),F15))</f>
-        <v>40800</v>
+        <v>3000</v>
       </c>
       <c r="K15" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L15),"Override",IF(COUNT(O15,Q15,S15,U15)&gt;0,"Low bid","Internal rate"))</f>
@@ -2731,53 +2881,52 @@
       <c r="T15" s="6"/>
       <c r="U15" s="27"/>
       <c r="V15" s="8" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="W15" s="14" t="n">
         <f aca="false">IF(M15="",F15,M15)</f>
-        <v>40800</v>
+        <v>3000</v>
       </c>
       <c r="X15" s="14" t="n">
         <f aca="false">J15-F15</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="22" t="n">
         <v>10</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>600</v>
       </c>
-      <c r="D16" s="28" t="n">
-        <f aca="false">WEEKS</f>
-        <v>24</v>
+      <c r="D16" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">C16*D16</f>
-        <v>14400</v>
+        <v>600</v>
       </c>
       <c r="G16" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J16/GRANDCAR)</f>
-        <v>0.0528647926758473</v>
+        <v>0.00205695707278004</v>
       </c>
       <c r="H16" s="14" t="n">
         <f aca="false">J16/(1-MARGIN)</f>
-        <v>24000</v>
+        <v>1000</v>
       </c>
       <c r="I16" s="14" t="n">
         <f aca="false">H16-J16</f>
-        <v>9600</v>
+        <v>400</v>
       </c>
       <c r="J16" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L16),L16,IF(COUNT(O16,Q16,S16,U16)&gt;0,MIN(O16,Q16,S16,U16),F16))</f>
-        <v>14400</v>
+        <v>600</v>
       </c>
       <c r="K16" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L16),"Override",IF(COUNT(O16,Q16,S16,U16)&gt;0,"Low bid","Internal rate"))</f>
@@ -2797,11 +2946,11 @@
       <c r="T16" s="6"/>
       <c r="U16" s="27"/>
       <c r="V16" s="8" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="W16" s="14" t="n">
         <f aca="false">IF(M16="",F16,M16)</f>
-        <v>14400</v>
+        <v>600</v>
       </c>
       <c r="X16" s="14" t="n">
         <f aca="false">J16-F16</f>
@@ -2813,37 +2962,36 @@
         <v>11</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C17" s="10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D17" s="28" t="n">
-        <f aca="false">WEEKS</f>
-        <v>24</v>
+        <v>4500</v>
+      </c>
+      <c r="D17" s="24" t="n">
+        <v>1</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">C17*D17</f>
-        <v>24000</v>
+        <v>4500</v>
       </c>
       <c r="G17" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J17/GRANDCAR)</f>
-        <v>0.0881079877930788</v>
+        <v>0.0154271780458503</v>
       </c>
       <c r="H17" s="14" t="n">
         <f aca="false">J17/(1-MARGIN)</f>
-        <v>40000</v>
+        <v>7500</v>
       </c>
       <c r="I17" s="14" t="n">
         <f aca="false">H17-J17</f>
-        <v>16000</v>
+        <v>3000</v>
       </c>
       <c r="J17" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L17),L17,IF(COUNT(O17,Q17,S17,U17)&gt;0,MIN(O17,Q17,S17,U17),F17))</f>
-        <v>24000</v>
+        <v>4500</v>
       </c>
       <c r="K17" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L17),"Override",IF(COUNT(O17,Q17,S17,U17)&gt;0,"Low bid","Internal rate"))</f>
@@ -2863,1130 +3011,1115 @@
       <c r="T17" s="6"/>
       <c r="U17" s="27"/>
       <c r="V17" s="8" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="W17" s="14" t="n">
         <f aca="false">IF(M17="",F17,M17)</f>
-        <v>24000</v>
+        <v>4500</v>
       </c>
       <c r="X17" s="14" t="n">
         <f aca="false">J17-F17</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="13" t="n">
-        <f aca="false">SUM(F7:F17)</f>
-        <v>100700</v>
-      </c>
-      <c r="G18" s="17" t="n">
+    <row r="18" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="23" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <v>1700</v>
+      </c>
+      <c r="D18" s="28" t="n">
+        <f aca="false">WEEKS</f>
+        <v>27</v>
+      </c>
+      <c r="E18" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="14" t="n">
+        <f aca="false">C18*D18</f>
+        <v>45900</v>
+      </c>
+      <c r="G18" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J18/GRANDCAR)</f>
-        <v>0.369686432115127</v>
-      </c>
-      <c r="H18" s="13" t="n">
-        <f aca="false">SUM(H7:H17)</f>
-        <v>167833.333333333</v>
-      </c>
-      <c r="I18" s="13" t="n">
-        <f aca="false">SUM(I7:I17)</f>
-        <v>67133.3333333333</v>
-      </c>
-      <c r="J18" s="13" t="n">
-        <f aca="false">SUM(J7:J17)</f>
-        <v>100700</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20"/>
-      <c r="B20" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="20"/>
-      <c r="D20" s="20"/>
-      <c r="E20" s="20"/>
-      <c r="F20" s="20"/>
-      <c r="G20" s="20"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="20"/>
-      <c r="N20" s="20"/>
-      <c r="O20" s="20"/>
-      <c r="P20" s="20"/>
-      <c r="Q20" s="20"/>
-      <c r="R20" s="20"/>
-      <c r="S20" s="20"/>
-      <c r="T20" s="20"/>
-      <c r="U20" s="20"/>
-      <c r="V20" s="20"/>
-    </row>
-    <row r="21" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B21" s="23" t="s">
-        <v>108</v>
-      </c>
-      <c r="C21" s="10" t="n">
+        <v>0.157357216067673</v>
+      </c>
+      <c r="H18" s="14" t="n">
+        <f aca="false">J18/(1-MARGIN)</f>
+        <v>76500</v>
+      </c>
+      <c r="I18" s="14" t="n">
+        <f aca="false">H18-J18</f>
+        <v>30600</v>
+      </c>
+      <c r="J18" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L18),L18,IF(COUNT(O18,Q18,S18,U18)&gt;0,MIN(O18,Q18,S18,U18),F18))</f>
+        <v>45900</v>
+      </c>
+      <c r="K18" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L18),"Override",IF(COUNT(O18,Q18,S18,U18)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L18" s="10"/>
+      <c r="M18" s="14" t="str">
+        <f aca="false">IF(COUNT(O18,Q18,S18,U18)=0,"",MIN(O18,Q18,S18,U18))</f>
+        <v/>
+      </c>
+      <c r="N18" s="6"/>
+      <c r="O18" s="27"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="27"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="27"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="27"/>
+      <c r="V18" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="W18" s="14" t="n">
+        <f aca="false">IF(M18="",F18,M18)</f>
+        <v>45900</v>
+      </c>
+      <c r="X18" s="14" t="n">
+        <f aca="false">J18-F18</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="23" t="s">
+        <v>116</v>
+      </c>
+      <c r="C19" s="10" t="n">
+        <v>600</v>
+      </c>
+      <c r="D19" s="28" t="n">
+        <f aca="false">WEEKS</f>
+        <v>27</v>
+      </c>
+      <c r="E19" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="F19" s="14" t="n">
+        <f aca="false">C19*D19</f>
+        <v>16200</v>
+      </c>
+      <c r="G19" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J19/GRANDCAR)</f>
+        <v>0.0555378409650612</v>
+      </c>
+      <c r="H19" s="14" t="n">
+        <f aca="false">J19/(1-MARGIN)</f>
+        <v>27000</v>
+      </c>
+      <c r="I19" s="14" t="n">
+        <f aca="false">H19-J19</f>
+        <v>10800</v>
+      </c>
+      <c r="J19" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L19),L19,IF(COUNT(O19,Q19,S19,U19)&gt;0,MIN(O19,Q19,S19,U19),F19))</f>
+        <v>16200</v>
+      </c>
+      <c r="K19" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L19),"Override",IF(COUNT(O19,Q19,S19,U19)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L19" s="10"/>
+      <c r="M19" s="14" t="str">
+        <f aca="false">IF(COUNT(O19,Q19,S19,U19)=0,"",MIN(O19,Q19,S19,U19))</f>
+        <v/>
+      </c>
+      <c r="N19" s="6"/>
+      <c r="O19" s="27"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="27"/>
+      <c r="R19" s="6"/>
+      <c r="S19" s="27"/>
+      <c r="T19" s="6"/>
+      <c r="U19" s="27"/>
+      <c r="V19" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="W19" s="14" t="n">
+        <f aca="false">IF(M19="",F19,M19)</f>
+        <v>16200</v>
+      </c>
+      <c r="X19" s="14" t="n">
+        <f aca="false">J19-F19</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="23" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <f aca="false">WEEKS</f>
+        <v>27</v>
+      </c>
+      <c r="E20" s="22" t="s">
+        <v>114</v>
+      </c>
+      <c r="F20" s="14" t="n">
+        <f aca="false">C20*D20</f>
+        <v>27000</v>
+      </c>
+      <c r="G20" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J20/GRANDCAR)</f>
+        <v>0.092563068275102</v>
+      </c>
+      <c r="H20" s="14" t="n">
+        <f aca="false">J20/(1-MARGIN)</f>
+        <v>45000</v>
+      </c>
+      <c r="I20" s="14" t="n">
+        <f aca="false">H20-J20</f>
+        <v>18000</v>
+      </c>
+      <c r="J20" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L20),L20,IF(COUNT(O20,Q20,S20,U20)&gt;0,MIN(O20,Q20,S20,U20),F20))</f>
+        <v>27000</v>
+      </c>
+      <c r="K20" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L20),"Override",IF(COUNT(O20,Q20,S20,U20)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L20" s="10"/>
+      <c r="M20" s="14" t="str">
+        <f aca="false">IF(COUNT(O20,Q20,S20,U20)=0,"",MIN(O20,Q20,S20,U20))</f>
+        <v/>
+      </c>
+      <c r="N20" s="6"/>
+      <c r="O20" s="27"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="27"/>
+      <c r="R20" s="6"/>
+      <c r="S20" s="27"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="27"/>
+      <c r="V20" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="W20" s="14" t="n">
+        <f aca="false">IF(M20="",F20,M20)</f>
+        <v>27000</v>
+      </c>
+      <c r="X20" s="14" t="n">
+        <f aca="false">J20-F20</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="F21" s="13" t="n">
+        <f aca="false">SUM(F7:F20)</f>
+        <v>118000</v>
+      </c>
+      <c r="G21" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J21/GRANDCAR)</f>
+        <v>0.404534890980075</v>
+      </c>
+      <c r="H21" s="13" t="n">
+        <f aca="false">SUM(H7:H20)</f>
+        <v>196666.666666667</v>
+      </c>
+      <c r="I21" s="13" t="n">
+        <f aca="false">SUM(I7:I20)</f>
+        <v>78666.6666666667</v>
+      </c>
+      <c r="J21" s="13" t="n">
+        <f aca="false">SUM(J7:J20)</f>
+        <v>118000</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="20"/>
+      <c r="B23" s="21" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="20"/>
+      <c r="D23" s="20"/>
+      <c r="E23" s="20"/>
+      <c r="F23" s="20"/>
+      <c r="G23" s="20"/>
+      <c r="H23" s="20"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="20"/>
+      <c r="O23" s="20"/>
+      <c r="P23" s="20"/>
+      <c r="Q23" s="20"/>
+      <c r="R23" s="20"/>
+      <c r="S23" s="20"/>
+      <c r="T23" s="20"/>
+      <c r="U23" s="20"/>
+      <c r="V23" s="20"/>
+    </row>
+    <row r="24" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B24" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="D21" s="24" t="n">
+      <c r="D24" s="24" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F21" s="14" t="n">
-        <f aca="false">C21*D21</f>
+      <c r="E24" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F24" s="14" t="n">
+        <f aca="false">C24*D24</f>
         <v>2000</v>
       </c>
-      <c r="G21" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J21/GRANDCAR)</f>
-        <v>0.0073423323160899</v>
-      </c>
-      <c r="H21" s="14" t="n">
-        <f aca="false">J21/(1-MARGIN)</f>
+      <c r="G24" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J24/GRANDCAR)</f>
+        <v>0.00685652357593348</v>
+      </c>
+      <c r="H24" s="14" t="n">
+        <f aca="false">J24/(1-MARGIN)</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="I21" s="14" t="n">
-        <f aca="false">H21-J21</f>
+      <c r="I24" s="14" t="n">
+        <f aca="false">H24-J24</f>
         <v>1333.33333333333</v>
       </c>
-      <c r="J21" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L21),L21,IF(COUNT(O21,Q21,S21,U21)&gt;0,MIN(O21,Q21,S21,U21),F21))</f>
+      <c r="J24" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L24),L24,IF(COUNT(O24,Q24,S24,U24)&gt;0,MIN(O24,Q24,S24,U24),F24))</f>
         <v>2000</v>
       </c>
-      <c r="K21" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L21),"Override",IF(COUNT(O21,Q21,S21,U21)&gt;0,"Low bid","Internal rate"))</f>
+      <c r="K24" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L24),"Override",IF(COUNT(O24,Q24,S24,U24)&gt;0,"Low bid","Internal rate"))</f>
         <v>Internal rate</v>
       </c>
-      <c r="L21" s="10"/>
-      <c r="M21" s="14" t="str">
-        <f aca="false">IF(COUNT(O21,Q21,S21,U21)=0,"",MIN(O21,Q21,S21,U21))</f>
+      <c r="L24" s="10"/>
+      <c r="M24" s="14" t="str">
+        <f aca="false">IF(COUNT(O24,Q24,S24,U24)=0,"",MIN(O24,Q24,S24,U24))</f>
         <v/>
       </c>
-      <c r="N21" s="29" t="s">
-        <v>110</v>
-      </c>
-      <c r="O21" s="27"/>
-      <c r="P21" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="Q21" s="27"/>
-      <c r="R21" s="29" t="s">
-        <v>112</v>
-      </c>
-      <c r="S21" s="27"/>
-      <c r="T21" s="6"/>
-      <c r="U21" s="27"/>
-      <c r="V21" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="W21" s="14" t="n">
-        <f aca="false">IF(M21="",F21,M21)</f>
+      <c r="N24" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="O24" s="27"/>
+      <c r="P24" s="29" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="29" t="s">
+        <v>126</v>
+      </c>
+      <c r="S24" s="27"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="27"/>
+      <c r="V24" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="W24" s="14" t="n">
+        <f aca="false">IF(M24="",F24,M24)</f>
         <v>2000</v>
       </c>
-      <c r="X21" s="14" t="n">
-        <f aca="false">J21-F21</f>
+      <c r="X24" s="14" t="n">
+        <f aca="false">J24-F24</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="B22" s="23" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="30" t="n">
+    <row r="25" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B25" s="23" t="s">
+        <v>128</v>
+      </c>
+      <c r="C25" s="30" t="n">
         <v>41.2</v>
       </c>
-      <c r="D22" s="24" t="n">
+      <c r="D25" s="24" t="n">
         <v>85</v>
       </c>
-      <c r="E22" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="14" t="n">
-        <f aca="false">C22*D22</f>
+      <c r="E25" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F25" s="14" t="n">
+        <f aca="false">C25*D25</f>
         <v>3502</v>
       </c>
-      <c r="G22" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J22/GRANDCAR)</f>
-        <v>0.0128564238854734</v>
-      </c>
-      <c r="H22" s="14" t="n">
-        <f aca="false">J22/(1-MARGIN)</f>
+      <c r="G25" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J25/GRANDCAR)</f>
+        <v>0.0120057727814595</v>
+      </c>
+      <c r="H25" s="14" t="n">
+        <f aca="false">J25/(1-MARGIN)</f>
         <v>5836.66666666667</v>
       </c>
-      <c r="I22" s="14" t="n">
-        <f aca="false">H22-J22</f>
+      <c r="I25" s="14" t="n">
+        <f aca="false">H25-J25</f>
         <v>2334.66666666667</v>
       </c>
-      <c r="J22" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L22),L22,IF(COUNT(O22,Q22,S22,U22)&gt;0,MIN(O22,Q22,S22,U22),F22))</f>
+      <c r="J25" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L25),L25,IF(COUNT(O25,Q25,S25,U25)&gt;0,MIN(O25,Q25,S25,U25),F25))</f>
         <v>3502</v>
       </c>
-      <c r="K22" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L22),"Override",IF(COUNT(O22,Q22,S22,U22)&gt;0,"Low bid","Internal rate"))</f>
+      <c r="K25" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L25),"Override",IF(COUNT(O25,Q25,S25,U25)&gt;0,"Low bid","Internal rate"))</f>
         <v>Internal rate</v>
       </c>
-      <c r="L22" s="10"/>
-      <c r="M22" s="14" t="str">
-        <f aca="false">IF(COUNT(O22,Q22,S22,U22)=0,"",MIN(O22,Q22,S22,U22))</f>
+      <c r="L25" s="10"/>
+      <c r="M25" s="14" t="str">
+        <f aca="false">IF(COUNT(O25,Q25,S25,U25)=0,"",MIN(O25,Q25,S25,U25))</f>
         <v/>
       </c>
-      <c r="N22" s="6"/>
-      <c r="O22" s="27"/>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="27"/>
-      <c r="R22" s="6"/>
-      <c r="S22" s="27"/>
-      <c r="T22" s="6"/>
-      <c r="U22" s="27"/>
-      <c r="V22" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="W22" s="14" t="n">
-        <f aca="false">IF(M22="",F22,M22)</f>
+      <c r="N25" s="6"/>
+      <c r="O25" s="27"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="27"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="27"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="27"/>
+      <c r="V25" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="W25" s="14" t="n">
+        <f aca="false">IF(M25="",F25,M25)</f>
         <v>3502</v>
       </c>
-      <c r="X22" s="14" t="n">
-        <f aca="false">J22-F22</f>
+      <c r="X25" s="14" t="n">
+        <f aca="false">J25-F25</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="n">
+    <row r="26" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B26" s="23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C26" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B23" s="23" t="s">
-        <v>117</v>
-      </c>
-      <c r="C23" s="30" t="n">
-        <v>14</v>
-      </c>
-      <c r="D23" s="24" t="n">
+      <c r="D26" s="24" t="n">
         <v>85</v>
       </c>
-      <c r="E23" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="F23" s="14" t="n">
-        <f aca="false">C23*D23</f>
+      <c r="E26" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F26" s="14" t="n">
+        <f aca="false">C26*D26</f>
         <v>1190</v>
       </c>
-      <c r="G23" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J23/GRANDCAR)</f>
-        <v>0.00436868772807349</v>
-      </c>
-      <c r="H23" s="14" t="n">
-        <f aca="false">J23/(1-MARGIN)</f>
+      <c r="G26" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J26/GRANDCAR)</f>
+        <v>0.00407963152768042</v>
+      </c>
+      <c r="H26" s="14" t="n">
+        <f aca="false">J26/(1-MARGIN)</f>
         <v>1983.33333333333</v>
       </c>
-      <c r="I23" s="14" t="n">
-        <f aca="false">H23-J23</f>
+      <c r="I26" s="14" t="n">
+        <f aca="false">H26-J26</f>
         <v>793.333333333334</v>
       </c>
-      <c r="J23" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L23),L23,IF(COUNT(O23,Q23,S23,U23)&gt;0,MIN(O23,Q23,S23,U23),F23))</f>
+      <c r="J26" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L26),L26,IF(COUNT(O26,Q26,S26,U26)&gt;0,MIN(O26,Q26,S26,U26),F26))</f>
         <v>1190</v>
       </c>
-      <c r="K23" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L23),"Override",IF(COUNT(O23,Q23,S23,U23)&gt;0,"Low bid","Internal rate"))</f>
+      <c r="K26" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L26),"Override",IF(COUNT(O26,Q26,S26,U26)&gt;0,"Low bid","Internal rate"))</f>
         <v>Internal rate</v>
       </c>
-      <c r="L23" s="10"/>
-      <c r="M23" s="14" t="str">
-        <f aca="false">IF(COUNT(O23,Q23,S23,U23)=0,"",MIN(O23,Q23,S23,U23))</f>
+      <c r="L26" s="10"/>
+      <c r="M26" s="14" t="str">
+        <f aca="false">IF(COUNT(O26,Q26,S26,U26)=0,"",MIN(O26,Q26,S26,U26))</f>
         <v/>
       </c>
-      <c r="N23" s="6"/>
-      <c r="O23" s="27"/>
-      <c r="P23" s="6"/>
-      <c r="Q23" s="27"/>
-      <c r="R23" s="6"/>
-      <c r="S23" s="27"/>
-      <c r="T23" s="6"/>
-      <c r="U23" s="27"/>
-      <c r="V23" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="W23" s="14" t="n">
-        <f aca="false">IF(M23="",F23,M23)</f>
+      <c r="N26" s="6"/>
+      <c r="O26" s="27"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="27"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="27"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="27"/>
+      <c r="V26" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="W26" s="14" t="n">
+        <f aca="false">IF(M26="",F26,M26)</f>
         <v>1190</v>
       </c>
-      <c r="X23" s="14" t="n">
-        <f aca="false">J23-F23</f>
+      <c r="X26" s="14" t="n">
+        <f aca="false">J26-F26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="12" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="13" t="n">
-        <f aca="false">SUM(F21:F23)</f>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="F27" s="13" t="n">
+        <f aca="false">SUM(F24:F26)</f>
         <v>6692</v>
       </c>
-      <c r="G24" s="17" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J24/GRANDCAR)</f>
-        <v>0.0245674439296368</v>
-      </c>
-      <c r="H24" s="13" t="n">
-        <f aca="false">SUM(H21:H23)</f>
+      <c r="G27" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J27/GRANDCAR)</f>
+        <v>0.0229419278850734</v>
+      </c>
+      <c r="H27" s="13" t="n">
+        <f aca="false">SUM(H24:H26)</f>
         <v>11153.3333333333</v>
       </c>
-      <c r="I24" s="13" t="n">
-        <f aca="false">SUM(I21:I23)</f>
+      <c r="I27" s="13" t="n">
+        <f aca="false">SUM(I24:I26)</f>
         <v>4461.33333333333</v>
       </c>
-      <c r="J24" s="13" t="n">
-        <f aca="false">SUM(J21:J23)</f>
+      <c r="J27" s="13" t="n">
+        <f aca="false">SUM(J24:J26)</f>
         <v>6692</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20"/>
-      <c r="B26" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
-      <c r="F26" s="20"/>
-      <c r="G26" s="20"/>
-      <c r="H26" s="20"/>
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="20"/>
-      <c r="N26" s="20"/>
-      <c r="O26" s="20"/>
-      <c r="P26" s="20"/>
-      <c r="Q26" s="20"/>
-      <c r="R26" s="20"/>
-      <c r="S26" s="20"/>
-      <c r="T26" s="20"/>
-      <c r="U26" s="20"/>
-      <c r="V26" s="20"/>
-    </row>
-    <row r="27" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B27" s="23" t="s">
-        <v>121</v>
-      </c>
-      <c r="C27" s="30" t="n">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="20"/>
+      <c r="B29" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="20"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="20"/>
+      <c r="N29" s="20"/>
+      <c r="O29" s="20"/>
+      <c r="P29" s="20"/>
+      <c r="Q29" s="20"/>
+      <c r="R29" s="20"/>
+      <c r="S29" s="20"/>
+      <c r="T29" s="20"/>
+      <c r="U29" s="20"/>
+      <c r="V29" s="20"/>
+    </row>
+    <row r="30" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="22" t="n">
+        <v>18</v>
+      </c>
+      <c r="B30" s="23" t="s">
+        <v>135</v>
+      </c>
+      <c r="C30" s="30" t="n">
         <v>20</v>
       </c>
-      <c r="D27" s="24" t="n">
+      <c r="D30" s="24" t="n">
         <v>693</v>
       </c>
-      <c r="E27" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="F27" s="14" t="n">
-        <f aca="false">C27*D27</f>
+      <c r="E30" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <f aca="false">C30*D30</f>
         <v>13860</v>
       </c>
-      <c r="G27" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J27/GRANDCAR)</f>
-        <v>0.0398285183602913</v>
-      </c>
-      <c r="H27" s="14" t="n">
-        <f aca="false">J27/(1-MARGIN)</f>
+      <c r="G30" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J30/GRANDCAR)</f>
+        <v>0.037193246420269</v>
+      </c>
+      <c r="H30" s="14" t="n">
+        <f aca="false">J30/(1-MARGIN)</f>
         <v>18081.6833333333</v>
       </c>
-      <c r="I27" s="14" t="n">
-        <f aca="false">H27-J27</f>
+      <c r="I30" s="14" t="n">
+        <f aca="false">H30-J30</f>
         <v>7232.67333333333</v>
       </c>
-      <c r="J27" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L27),L27,IF(COUNT(O27,Q27,S27,U27)&gt;0,MIN(O27,Q27,S27,U27),F27))</f>
+      <c r="J30" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L30),L30,IF(COUNT(O30,Q30,S30,U30)&gt;0,MIN(O30,Q30,S30,U30),F30))</f>
         <v>10849.01</v>
       </c>
-      <c r="K27" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L27),"Override",IF(COUNT(O27,Q27,S27,U27)&gt;0,"Low bid","Internal rate"))</f>
+      <c r="K30" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L30),"Override",IF(COUNT(O30,Q30,S30,U30)&gt;0,"Low bid","Internal rate"))</f>
         <v>Override</v>
       </c>
-      <c r="L27" s="10" t="n">
+      <c r="L30" s="10" t="n">
         <v>10849.01</v>
       </c>
-      <c r="M27" s="14" t="n">
-        <f aca="false">IF(COUNT(O27,Q27,S27,U27)=0,"",MIN(O27,Q27,S27,U27))</f>
+      <c r="M30" s="14" t="n">
+        <f aca="false">IF(COUNT(O30,Q30,S30,U30)=0,"",MIN(O30,Q30,S30,U30))</f>
         <v>9792.11</v>
       </c>
-      <c r="N27" s="29" t="s">
-        <v>122</v>
-      </c>
-      <c r="O27" s="10" t="n">
+      <c r="N30" s="29" t="s">
+        <v>136</v>
+      </c>
+      <c r="O30" s="10" t="n">
         <v>9792.11</v>
       </c>
-      <c r="P27" s="29" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q27" s="10" t="n">
+      <c r="P30" s="29" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q30" s="10" t="n">
         <v>10849.01</v>
       </c>
-      <c r="R27" s="29" t="s">
-        <v>124</v>
-      </c>
-      <c r="S27" s="27"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="27"/>
-      <c r="V27" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="W27" s="14" t="n">
-        <f aca="false">IF(M27="",F27,M27)</f>
+      <c r="R30" s="29" t="s">
+        <v>138</v>
+      </c>
+      <c r="S30" s="27"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="27"/>
+      <c r="V30" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="W30" s="14" t="n">
+        <f aca="false">IF(M30="",F30,M30)</f>
         <v>9792.11</v>
       </c>
-      <c r="X27" s="14" t="n">
-        <f aca="false">J27-F27</f>
+      <c r="X30" s="14" t="n">
+        <f aca="false">J30-F30</f>
         <v>-3010.99</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B28" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="C28" s="30" t="n">
+    <row r="31" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="22" t="n">
+        <v>19</v>
+      </c>
+      <c r="B31" s="23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C31" s="30" t="n">
         <v>22</v>
       </c>
-      <c r="D28" s="24" t="n">
+      <c r="D31" s="24" t="n">
         <v>693</v>
       </c>
-      <c r="E28" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="F28" s="14" t="n">
-        <f aca="false">C28*D28</f>
+      <c r="E31" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <f aca="false">C31*D31</f>
         <v>15246</v>
       </c>
-      <c r="G28" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J28/GRANDCAR)</f>
-        <v>0.0679165739238316</v>
-      </c>
-      <c r="H28" s="14" t="n">
-        <f aca="false">J28/(1-MARGIN)</f>
+      <c r="G31" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J31/GRANDCAR)</f>
+        <v>0.0634228430773847</v>
+      </c>
+      <c r="H31" s="14" t="n">
+        <f aca="false">J31/(1-MARGIN)</f>
         <v>30833.3333333333</v>
       </c>
-      <c r="I28" s="14" t="n">
-        <f aca="false">H28-J28</f>
+      <c r="I31" s="14" t="n">
+        <f aca="false">H31-J31</f>
         <v>12333.3333333333</v>
       </c>
-      <c r="J28" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L28),L28,IF(COUNT(O28,Q28,S28,U28)&gt;0,MIN(O28,Q28,S28,U28),F28))</f>
+      <c r="J31" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L31),L31,IF(COUNT(O31,Q31,S31,U31)&gt;0,MIN(O31,Q31,S31,U31),F31))</f>
         <v>18500</v>
       </c>
-      <c r="K28" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L28),"Override",IF(COUNT(O28,Q28,S28,U28)&gt;0,"Low bid","Internal rate"))</f>
+      <c r="K31" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L31),"Override",IF(COUNT(O31,Q31,S31,U31)&gt;0,"Low bid","Internal rate"))</f>
         <v>Override</v>
       </c>
-      <c r="L28" s="10" t="n">
+      <c r="L31" s="10" t="n">
         <v>18500</v>
       </c>
-      <c r="M28" s="14" t="n">
-        <f aca="false">IF(COUNT(O28,Q28,S28,U28)=0,"",MIN(O28,Q28,S28,U28))</f>
+      <c r="M31" s="14" t="n">
+        <f aca="false">IF(COUNT(O31,Q31,S31,U31)=0,"",MIN(O31,Q31,S31,U31))</f>
         <v>18000</v>
       </c>
-      <c r="N28" s="29" t="s">
-        <v>127</v>
-      </c>
-      <c r="O28" s="10" t="n">
+      <c r="N31" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="O31" s="10" t="n">
         <v>18000</v>
       </c>
-      <c r="P28" s="29" t="s">
-        <v>128</v>
-      </c>
-      <c r="Q28" s="10" t="n">
+      <c r="P31" s="29" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q31" s="10" t="n">
         <v>29000</v>
       </c>
-      <c r="R28" s="29" t="s">
-        <v>129</v>
-      </c>
-      <c r="S28" s="10" t="n">
+      <c r="R31" s="29" t="s">
+        <v>143</v>
+      </c>
+      <c r="S31" s="10" t="n">
         <v>18500</v>
       </c>
-      <c r="T28" s="6"/>
-      <c r="U28" s="27"/>
-      <c r="V28" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="W28" s="14" t="n">
-        <f aca="false">IF(M28="",F28,M28)</f>
+      <c r="T31" s="6"/>
+      <c r="U31" s="27"/>
+      <c r="V31" s="8" t="s">
+        <v>144</v>
+      </c>
+      <c r="W31" s="14" t="n">
+        <f aca="false">IF(M31="",F31,M31)</f>
         <v>18000</v>
       </c>
-      <c r="X28" s="14" t="n">
-        <f aca="false">J28-F28</f>
+      <c r="X31" s="14" t="n">
+        <f aca="false">J31-F31</f>
         <v>3254</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" s="13" t="n">
-        <f aca="false">SUM(F27:F28)</f>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="F32" s="13" t="n">
+        <f aca="false">SUM(F30:F31)</f>
         <v>29106</v>
       </c>
-      <c r="G29" s="17" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J29/GRANDCAR)</f>
-        <v>0.107745092284123</v>
-      </c>
-      <c r="H29" s="13" t="n">
-        <f aca="false">SUM(H27:H28)</f>
+      <c r="G32" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J32/GRANDCAR)</f>
+        <v>0.100616089497654</v>
+      </c>
+      <c r="H32" s="13" t="n">
+        <f aca="false">SUM(H30:H31)</f>
         <v>48915.0166666667</v>
       </c>
-      <c r="I29" s="13" t="n">
-        <f aca="false">SUM(I27:I28)</f>
+      <c r="I32" s="13" t="n">
+        <f aca="false">SUM(I30:I31)</f>
         <v>19566.0066666667</v>
       </c>
-      <c r="J29" s="13" t="n">
-        <f aca="false">SUM(J27:J28)</f>
+      <c r="J32" s="13" t="n">
+        <f aca="false">SUM(J30:J31)</f>
         <v>29349.01</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20"/>
-      <c r="B31" s="21" t="s">
-        <v>132</v>
-      </c>
-      <c r="C31" s="20"/>
-      <c r="D31" s="20"/>
-      <c r="E31" s="20"/>
-      <c r="F31" s="20"/>
-      <c r="G31" s="20"/>
-      <c r="H31" s="20"/>
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="20"/>
-      <c r="N31" s="20"/>
-      <c r="O31" s="20"/>
-      <c r="P31" s="20"/>
-      <c r="Q31" s="20"/>
-      <c r="R31" s="20"/>
-      <c r="S31" s="20"/>
-      <c r="T31" s="20"/>
-      <c r="U31" s="20"/>
-      <c r="V31" s="20"/>
-    </row>
-    <row r="32" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B32" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="C32" s="30" t="n">
-        <v>8</v>
-      </c>
-      <c r="D32" s="24" t="n">
-        <v>1200</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <f aca="false">C32*D32</f>
-        <v>9600</v>
-      </c>
-      <c r="G32" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J32/GRANDCAR)</f>
-        <v>0.0226694510259276</v>
-      </c>
-      <c r="H32" s="14" t="n">
-        <f aca="false">J32/(1-MARGIN)</f>
-        <v>10291.6666666667</v>
-      </c>
-      <c r="I32" s="14" t="n">
-        <f aca="false">H32-J32</f>
-        <v>4116.66666666667</v>
-      </c>
-      <c r="J32" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L32),L32,IF(COUNT(O32,Q32,S32,U32)&gt;0,MIN(O32,Q32,S32,U32),F32))</f>
-        <v>6175</v>
-      </c>
-      <c r="K32" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L32),"Override",IF(COUNT(O32,Q32,S32,U32)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Override</v>
-      </c>
-      <c r="L32" s="10" t="n">
-        <v>6175</v>
-      </c>
-      <c r="M32" s="14" t="n">
-        <f aca="false">IF(COUNT(O32,Q32,S32,U32)=0,"",MIN(O32,Q32,S32,U32))</f>
-        <v>3800</v>
-      </c>
-      <c r="N32" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="O32" s="10" t="n">
-        <v>6175</v>
-      </c>
-      <c r="P32" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q32" s="10" t="n">
-        <v>3800</v>
-      </c>
-      <c r="R32" s="29" t="s">
-        <v>136</v>
-      </c>
-      <c r="S32" s="10" t="n">
-        <v>5500</v>
-      </c>
-      <c r="T32" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="U32" s="10" t="n">
-        <v>6350</v>
-      </c>
-      <c r="V32" s="8" t="s">
-        <v>138</v>
-      </c>
-      <c r="W32" s="14" t="n">
-        <f aca="false">IF(M32="",F32,M32)</f>
-        <v>3800</v>
-      </c>
-      <c r="X32" s="14" t="n">
-        <f aca="false">J32-F32</f>
-        <v>-3425</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22" t="n">
-        <v>18</v>
-      </c>
-      <c r="B33" s="23" t="s">
-        <v>139</v>
-      </c>
-      <c r="C33" s="10" t="n">
-        <v>9400</v>
-      </c>
-      <c r="D33" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F33" s="14" t="n">
-        <f aca="false">C33*D33</f>
-        <v>9400</v>
-      </c>
-      <c r="G33" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J33/GRANDCAR)</f>
-        <v>0.0305624582657242</v>
-      </c>
-      <c r="H33" s="14" t="n">
-        <f aca="false">J33/(1-MARGIN)</f>
-        <v>13875</v>
-      </c>
-      <c r="I33" s="14" t="n">
-        <f aca="false">H33-J33</f>
-        <v>5550</v>
-      </c>
-      <c r="J33" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L33),L33,IF(COUNT(O33,Q33,S33,U33)&gt;0,MIN(O33,Q33,S33,U33),F33))</f>
-        <v>8325</v>
-      </c>
-      <c r="K33" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L33),"Override",IF(COUNT(O33,Q33,S33,U33)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Override</v>
-      </c>
-      <c r="L33" s="10" t="n">
-        <v>8325</v>
-      </c>
-      <c r="M33" s="14" t="n">
-        <f aca="false">IF(COUNT(O33,Q33,S33,U33)=0,"",MIN(O33,Q33,S33,U33))</f>
-        <v>3800</v>
-      </c>
-      <c r="N33" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="O33" s="10" t="n">
-        <v>8325</v>
-      </c>
-      <c r="P33" s="29" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q33" s="10" t="n">
-        <v>3800</v>
-      </c>
-      <c r="R33" s="6"/>
-      <c r="S33" s="27"/>
-      <c r="T33" s="6"/>
-      <c r="U33" s="27"/>
-      <c r="V33" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="W33" s="14" t="n">
-        <f aca="false">IF(M33="",F33,M33)</f>
-        <v>3800</v>
-      </c>
-      <c r="X33" s="14" t="n">
-        <f aca="false">J33-F33</f>
-        <v>-1075</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="22" t="n">
-        <v>19</v>
-      </c>
-      <c r="B34" s="23" t="s">
-        <v>141</v>
-      </c>
-      <c r="C34" s="10" t="n">
-        <v>28600</v>
-      </c>
-      <c r="D34" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F34" s="14" t="n">
-        <f aca="false">C34*D34</f>
-        <v>28600</v>
-      </c>
-      <c r="G34" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J34/GRANDCAR)</f>
-        <v>0.132161981689618</v>
-      </c>
-      <c r="H34" s="14" t="n">
-        <f aca="false">J34/(1-MARGIN)</f>
-        <v>60000</v>
-      </c>
-      <c r="I34" s="14" t="n">
-        <f aca="false">H34-J34</f>
-        <v>24000</v>
-      </c>
-      <c r="J34" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L34),L34,IF(COUNT(O34,Q34,S34,U34)&gt;0,MIN(O34,Q34,S34,U34),F34))</f>
-        <v>36000</v>
-      </c>
-      <c r="K34" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L34),"Override",IF(COUNT(O34,Q34,S34,U34)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Low bid</v>
-      </c>
-      <c r="L34" s="10"/>
-      <c r="M34" s="14" t="n">
-        <f aca="false">IF(COUNT(O34,Q34,S34,U34)=0,"",MIN(O34,Q34,S34,U34))</f>
-        <v>36000</v>
-      </c>
-      <c r="N34" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="O34" s="10" t="n">
-        <v>36000</v>
-      </c>
-      <c r="P34" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q34" s="27"/>
-      <c r="R34" s="6"/>
-      <c r="S34" s="27"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="27"/>
-      <c r="V34" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="W34" s="14" t="n">
-        <f aca="false">IF(M34="",F34,M34)</f>
-        <v>36000</v>
-      </c>
-      <c r="X34" s="14" t="n">
-        <f aca="false">J34-F34</f>
-        <v>7400</v>
-      </c>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="20"/>
+      <c r="B34" s="21" t="s">
+        <v>146</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
+      <c r="G34" s="20"/>
+      <c r="H34" s="20"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
+      <c r="N34" s="20"/>
+      <c r="O34" s="20"/>
+      <c r="P34" s="20"/>
+      <c r="Q34" s="20"/>
+      <c r="R34" s="20"/>
+      <c r="S34" s="20"/>
+      <c r="T34" s="20"/>
+      <c r="U34" s="20"/>
+      <c r="V34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="22" t="n">
         <v>20</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="C35" s="10" t="n">
-        <v>110</v>
+        <v>147</v>
+      </c>
+      <c r="C35" s="30" t="n">
+        <v>8</v>
       </c>
       <c r="D35" s="24" t="n">
-        <v>80</v>
+        <v>1200</v>
       </c>
       <c r="E35" s="22" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F35" s="14" t="n">
         <f aca="false">C35*D35</f>
-        <v>8800</v>
+        <v>9600</v>
       </c>
       <c r="G35" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J35/GRANDCAR)</f>
-        <v>0.0203566163463593</v>
+        <v>0.0211695165406946</v>
       </c>
       <c r="H35" s="14" t="n">
         <f aca="false">J35/(1-MARGIN)</f>
-        <v>9241.66666666667</v>
+        <v>10291.6666666667</v>
       </c>
       <c r="I35" s="14" t="n">
         <f aca="false">H35-J35</f>
-        <v>3696.66666666667</v>
+        <v>4116.66666666667</v>
       </c>
       <c r="J35" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L35),L35,IF(COUNT(O35,Q35,S35,U35)&gt;0,MIN(O35,Q35,S35,U35),F35))</f>
-        <v>5545</v>
+        <v>6175</v>
       </c>
       <c r="K35" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L35),"Override",IF(COUNT(O35,Q35,S35,U35)&gt;0,"Low bid","Internal rate"))</f>
         <v>Override</v>
       </c>
       <c r="L35" s="10" t="n">
-        <v>5545</v>
+        <v>6175</v>
       </c>
       <c r="M35" s="14" t="n">
         <f aca="false">IF(COUNT(O35,Q35,S35,U35)=0,"",MIN(O35,Q35,S35,U35))</f>
-        <v>5221.24</v>
+        <v>3800</v>
       </c>
       <c r="N35" s="29" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="O35" s="10" t="n">
-        <v>5545</v>
+        <v>6175</v>
       </c>
       <c r="P35" s="29" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="Q35" s="10" t="n">
-        <v>5221.24</v>
-      </c>
-      <c r="R35" s="6"/>
-      <c r="S35" s="27"/>
-      <c r="T35" s="6"/>
-      <c r="U35" s="27"/>
+        <v>3800</v>
+      </c>
+      <c r="R35" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="S35" s="10" t="n">
+        <v>5500</v>
+      </c>
+      <c r="T35" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="U35" s="10" t="n">
+        <v>6350</v>
+      </c>
       <c r="V35" s="8" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="W35" s="14" t="n">
         <f aca="false">IF(M35="",F35,M35)</f>
-        <v>5221.24</v>
+        <v>3800</v>
       </c>
       <c r="X35" s="14" t="n">
         <f aca="false">J35-F35</f>
+        <v>-3425</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B36" s="23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <v>9400</v>
+      </c>
+      <c r="D36" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F36" s="14" t="n">
+        <f aca="false">C36*D36</f>
+        <v>9400</v>
+      </c>
+      <c r="G36" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J36/GRANDCAR)</f>
+        <v>0.0285402793848231</v>
+      </c>
+      <c r="H36" s="14" t="n">
+        <f aca="false">J36/(1-MARGIN)</f>
+        <v>13875</v>
+      </c>
+      <c r="I36" s="14" t="n">
+        <f aca="false">H36-J36</f>
+        <v>5550</v>
+      </c>
+      <c r="J36" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L36),L36,IF(COUNT(O36,Q36,S36,U36)&gt;0,MIN(O36,Q36,S36,U36),F36))</f>
+        <v>8325</v>
+      </c>
+      <c r="K36" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L36),"Override",IF(COUNT(O36,Q36,S36,U36)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Override</v>
+      </c>
+      <c r="L36" s="10" t="n">
+        <v>8325</v>
+      </c>
+      <c r="M36" s="14" t="n">
+        <f aca="false">IF(COUNT(O36,Q36,S36,U36)=0,"",MIN(O36,Q36,S36,U36))</f>
+        <v>3800</v>
+      </c>
+      <c r="N36" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="O36" s="10" t="n">
+        <v>8325</v>
+      </c>
+      <c r="P36" s="29" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q36" s="10" t="n">
+        <v>3800</v>
+      </c>
+      <c r="R36" s="6"/>
+      <c r="S36" s="27"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="27"/>
+      <c r="V36" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="W36" s="14" t="n">
+        <f aca="false">IF(M36="",F36,M36)</f>
+        <v>3800</v>
+      </c>
+      <c r="X36" s="14" t="n">
+        <f aca="false">J36-F36</f>
+        <v>-1075</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="n">
+        <v>22</v>
+      </c>
+      <c r="B37" s="23" t="s">
+        <v>155</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <v>28600</v>
+      </c>
+      <c r="D37" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F37" s="14" t="n">
+        <f aca="false">C37*D37</f>
+        <v>28600</v>
+      </c>
+      <c r="G37" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J37/GRANDCAR)</f>
+        <v>0.123417424366803</v>
+      </c>
+      <c r="H37" s="14" t="n">
+        <f aca="false">J37/(1-MARGIN)</f>
+        <v>60000</v>
+      </c>
+      <c r="I37" s="14" t="n">
+        <f aca="false">H37-J37</f>
+        <v>24000</v>
+      </c>
+      <c r="J37" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L37),L37,IF(COUNT(O37,Q37,S37,U37)&gt;0,MIN(O37,Q37,S37,U37),F37))</f>
+        <v>36000</v>
+      </c>
+      <c r="K37" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L37),"Override",IF(COUNT(O37,Q37,S37,U37)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Low bid</v>
+      </c>
+      <c r="L37" s="10"/>
+      <c r="M37" s="14" t="n">
+        <f aca="false">IF(COUNT(O37,Q37,S37,U37)=0,"",MIN(O37,Q37,S37,U37))</f>
+        <v>36000</v>
+      </c>
+      <c r="N37" s="29" t="s">
+        <v>148</v>
+      </c>
+      <c r="O37" s="10" t="n">
+        <v>36000</v>
+      </c>
+      <c r="P37" s="29" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q37" s="27"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="27"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="27"/>
+      <c r="V37" s="8" t="s">
+        <v>157</v>
+      </c>
+      <c r="W37" s="14" t="n">
+        <f aca="false">IF(M37="",F37,M37)</f>
+        <v>36000</v>
+      </c>
+      <c r="X37" s="14" t="n">
+        <f aca="false">J37-F37</f>
+        <v>7400</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="22" t="n">
+        <v>23</v>
+      </c>
+      <c r="B38" s="23" t="s">
+        <v>158</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <v>110</v>
+      </c>
+      <c r="D38" s="24" t="n">
+        <v>80</v>
+      </c>
+      <c r="E38" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F38" s="14" t="n">
+        <f aca="false">C38*D38</f>
+        <v>8800</v>
+      </c>
+      <c r="G38" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J38/GRANDCAR)</f>
+        <v>0.0190097116142756</v>
+      </c>
+      <c r="H38" s="14" t="n">
+        <f aca="false">J38/(1-MARGIN)</f>
+        <v>9241.66666666667</v>
+      </c>
+      <c r="I38" s="14" t="n">
+        <f aca="false">H38-J38</f>
+        <v>3696.66666666667</v>
+      </c>
+      <c r="J38" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L38),L38,IF(COUNT(O38,Q38,S38,U38)&gt;0,MIN(O38,Q38,S38,U38),F38))</f>
+        <v>5545</v>
+      </c>
+      <c r="K38" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L38),"Override",IF(COUNT(O38,Q38,S38,U38)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Override</v>
+      </c>
+      <c r="L38" s="10" t="n">
+        <v>5545</v>
+      </c>
+      <c r="M38" s="14" t="n">
+        <f aca="false">IF(COUNT(O38,Q38,S38,U38)=0,"",MIN(O38,Q38,S38,U38))</f>
+        <v>5221.24</v>
+      </c>
+      <c r="N38" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="O38" s="10" t="n">
+        <v>5545</v>
+      </c>
+      <c r="P38" s="29" t="s">
+        <v>160</v>
+      </c>
+      <c r="Q38" s="10" t="n">
+        <v>5221.24</v>
+      </c>
+      <c r="R38" s="6"/>
+      <c r="S38" s="27"/>
+      <c r="T38" s="6"/>
+      <c r="U38" s="27"/>
+      <c r="V38" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="W38" s="14" t="n">
+        <f aca="false">IF(M38="",F38,M38)</f>
+        <v>5221.24</v>
+      </c>
+      <c r="X38" s="14" t="n">
+        <f aca="false">J38-F38</f>
         <v>-3255</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="12" t="s">
-        <v>148</v>
-      </c>
-      <c r="F36" s="13" t="n">
-        <f aca="false">SUM(F32:F35)</f>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="12" t="s">
+        <v>162</v>
+      </c>
+      <c r="F39" s="13" t="n">
+        <f aca="false">SUM(F35:F38)</f>
         <v>56400</v>
       </c>
-      <c r="G36" s="17" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J36/GRANDCAR)</f>
-        <v>0.205750507327629</v>
-      </c>
-      <c r="H36" s="13" t="n">
-        <f aca="false">SUM(H32:H35)</f>
+      <c r="G39" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J39/GRANDCAR)</f>
+        <v>0.192136931906596</v>
+      </c>
+      <c r="H39" s="13" t="n">
+        <f aca="false">SUM(H35:H38)</f>
         <v>93408.3333333333</v>
       </c>
-      <c r="I36" s="13" t="n">
-        <f aca="false">SUM(I32:I35)</f>
+      <c r="I39" s="13" t="n">
+        <f aca="false">SUM(I35:I38)</f>
         <v>37363.3333333333</v>
       </c>
-      <c r="J36" s="13" t="n">
-        <f aca="false">SUM(J32:J35)</f>
+      <c r="J39" s="13" t="n">
+        <f aca="false">SUM(J35:J38)</f>
         <v>56045</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20"/>
-      <c r="B38" s="21" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
-      <c r="F38" s="20"/>
-      <c r="G38" s="20"/>
-      <c r="H38" s="20"/>
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="20"/>
-      <c r="N38" s="20"/>
-      <c r="O38" s="20"/>
-      <c r="P38" s="20"/>
-      <c r="Q38" s="20"/>
-      <c r="R38" s="20"/>
-      <c r="S38" s="20"/>
-      <c r="T38" s="20"/>
-      <c r="U38" s="20"/>
-      <c r="V38" s="20"/>
-    </row>
-    <row r="39" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B39" s="23" t="s">
-        <v>150</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D39" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F39" s="14" t="n">
-        <f aca="false">C39*D39</f>
-        <v>10000</v>
-      </c>
-      <c r="G39" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J39/GRANDCAR)</f>
-        <v>0.0308377957275776</v>
-      </c>
-      <c r="H39" s="14" t="n">
-        <f aca="false">J39/(1-MARGIN)</f>
-        <v>14000</v>
-      </c>
-      <c r="I39" s="14" t="n">
-        <f aca="false">H39-J39</f>
-        <v>5600</v>
-      </c>
-      <c r="J39" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L39),L39,IF(COUNT(O39,Q39,S39,U39)&gt;0,MIN(O39,Q39,S39,U39),F39))</f>
-        <v>8400</v>
-      </c>
-      <c r="K39" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L39),"Override",IF(COUNT(O39,Q39,S39,U39)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Low bid</v>
-      </c>
-      <c r="L39" s="10"/>
-      <c r="M39" s="14" t="n">
-        <f aca="false">IF(COUNT(O39,Q39,S39,U39)=0,"",MIN(O39,Q39,S39,U39))</f>
-        <v>8400</v>
-      </c>
-      <c r="N39" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="O39" s="10" t="n">
-        <v>8400</v>
-      </c>
-      <c r="P39" s="29" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q39" s="10" t="n">
-        <v>12398</v>
-      </c>
-      <c r="R39" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="S39" s="10" t="n">
-        <v>13479</v>
-      </c>
-      <c r="T39" s="6"/>
-      <c r="U39" s="27"/>
-      <c r="V39" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="W39" s="14" t="n">
-        <f aca="false">IF(M39="",F39,M39)</f>
-        <v>8400</v>
-      </c>
-      <c r="X39" s="14" t="n">
-        <f aca="false">J39-F39</f>
-        <v>-1600</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="22" t="n">
-        <v>22</v>
-      </c>
-      <c r="B40" s="23" t="s">
-        <v>155</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <v>5500</v>
-      </c>
-      <c r="D40" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F40" s="14" t="n">
-        <f aca="false">C40*D40</f>
-        <v>5500</v>
-      </c>
-      <c r="G40" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J40/GRANDCAR)</f>
-        <v>0.0165202477112023</v>
-      </c>
-      <c r="H40" s="14" t="n">
-        <f aca="false">J40/(1-MARGIN)</f>
-        <v>7500</v>
-      </c>
-      <c r="I40" s="14" t="n">
-        <f aca="false">H40-J40</f>
-        <v>3000</v>
-      </c>
-      <c r="J40" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L40),L40,IF(COUNT(O40,Q40,S40,U40)&gt;0,MIN(O40,Q40,S40,U40),F40))</f>
-        <v>4500</v>
-      </c>
-      <c r="K40" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L40),"Override",IF(COUNT(O40,Q40,S40,U40)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Low bid</v>
-      </c>
-      <c r="L40" s="10"/>
-      <c r="M40" s="14" t="n">
-        <f aca="false">IF(COUNT(O40,Q40,S40,U40)=0,"",MIN(O40,Q40,S40,U40))</f>
-        <v>4500</v>
-      </c>
-      <c r="N40" s="29" t="s">
-        <v>156</v>
-      </c>
-      <c r="O40" s="10" t="n">
-        <v>4500</v>
-      </c>
-      <c r="P40" s="29" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q40" s="27"/>
-      <c r="R40" s="6"/>
-      <c r="S40" s="27"/>
-      <c r="T40" s="6"/>
-      <c r="U40" s="27"/>
-      <c r="V40" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="W40" s="14" t="n">
-        <f aca="false">IF(M40="",F40,M40)</f>
-        <v>4500</v>
-      </c>
-      <c r="X40" s="14" t="n">
-        <f aca="false">J40-F40</f>
-        <v>-1000</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="22" t="n">
-        <v>23</v>
-      </c>
-      <c r="B41" s="23" t="s">
-        <v>159</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <v>2000</v>
-      </c>
-      <c r="D41" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F41" s="14" t="n">
-        <f aca="false">C41*D41</f>
-        <v>2000</v>
-      </c>
-      <c r="G41" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J41/GRANDCAR)</f>
-        <v>0.0073423323160899</v>
-      </c>
-      <c r="H41" s="14" t="n">
-        <f aca="false">J41/(1-MARGIN)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="I41" s="14" t="n">
-        <f aca="false">H41-J41</f>
-        <v>1333.33333333333</v>
-      </c>
-      <c r="J41" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L41),L41,IF(COUNT(O41,Q41,S41,U41)&gt;0,MIN(O41,Q41,S41,U41),F41))</f>
-        <v>2000</v>
-      </c>
-      <c r="K41" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L41),"Override",IF(COUNT(O41,Q41,S41,U41)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Internal rate</v>
-      </c>
-      <c r="L41" s="10"/>
-      <c r="M41" s="14" t="str">
-        <f aca="false">IF(COUNT(O41,Q41,S41,U41)=0,"",MIN(O41,Q41,S41,U41))</f>
-        <v/>
-      </c>
-      <c r="N41" s="6"/>
-      <c r="O41" s="27"/>
-      <c r="P41" s="6"/>
-      <c r="Q41" s="27"/>
-      <c r="R41" s="6"/>
-      <c r="S41" s="27"/>
-      <c r="T41" s="6"/>
-      <c r="U41" s="27"/>
-      <c r="V41" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="W41" s="14" t="n">
-        <f aca="false">IF(M41="",F41,M41)</f>
-        <v>2000</v>
-      </c>
-      <c r="X41" s="14" t="n">
-        <f aca="false">J41-F41</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="20"/>
+      <c r="B41" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="C41" s="20"/>
+      <c r="D41" s="20"/>
+      <c r="E41" s="20"/>
+      <c r="F41" s="20"/>
+      <c r="G41" s="20"/>
+      <c r="H41" s="20"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="20"/>
+      <c r="N41" s="20"/>
+      <c r="O41" s="20"/>
+      <c r="P41" s="20"/>
+      <c r="Q41" s="20"/>
+      <c r="R41" s="20"/>
+      <c r="S41" s="20"/>
+      <c r="T41" s="20"/>
+      <c r="U41" s="20"/>
+      <c r="V41" s="20"/>
+    </row>
+    <row r="42" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="22" t="n">
         <v>24</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>161</v>
-      </c>
-      <c r="C42" s="30" t="n">
-        <v>3</v>
+        <v>164</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>10000</v>
       </c>
       <c r="D42" s="24" t="n">
-        <v>700</v>
+        <v>1</v>
       </c>
       <c r="E42" s="22" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="F42" s="14" t="n">
         <f aca="false">C42*D42</f>
-        <v>2100</v>
+        <v>10000</v>
       </c>
       <c r="G42" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J42/GRANDCAR)</f>
-        <v>0.00857951531135105</v>
+        <v>0.0287973990189206</v>
       </c>
       <c r="H42" s="14" t="n">
         <f aca="false">J42/(1-MARGIN)</f>
-        <v>3895</v>
+        <v>14000</v>
       </c>
       <c r="I42" s="14" t="n">
         <f aca="false">H42-J42</f>
-        <v>1558</v>
+        <v>5600</v>
       </c>
       <c r="J42" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L42),L42,IF(COUNT(O42,Q42,S42,U42)&gt;0,MIN(O42,Q42,S42,U42),F42))</f>
-        <v>2337</v>
+        <v>8400</v>
       </c>
       <c r="K42" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L42),"Override",IF(COUNT(O42,Q42,S42,U42)&gt;0,"Low bid","Internal rate"))</f>
@@ -3995,444 +4128,458 @@
       <c r="L42" s="10"/>
       <c r="M42" s="14" t="n">
         <f aca="false">IF(COUNT(O42,Q42,S42,U42)=0,"",MIN(O42,Q42,S42,U42))</f>
-        <v>2337</v>
+        <v>8400</v>
       </c>
       <c r="N42" s="29" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="O42" s="10" t="n">
-        <v>2337</v>
-      </c>
-      <c r="P42" s="6"/>
-      <c r="Q42" s="27"/>
-      <c r="R42" s="6"/>
-      <c r="S42" s="27"/>
+        <v>8400</v>
+      </c>
+      <c r="P42" s="29" t="s">
+        <v>166</v>
+      </c>
+      <c r="Q42" s="10" t="n">
+        <v>12398</v>
+      </c>
+      <c r="R42" s="29" t="s">
+        <v>167</v>
+      </c>
+      <c r="S42" s="10" t="n">
+        <v>13479</v>
+      </c>
       <c r="T42" s="6"/>
       <c r="U42" s="27"/>
       <c r="V42" s="8" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="W42" s="14" t="n">
         <f aca="false">IF(M42="",F42,M42)</f>
-        <v>2337</v>
+        <v>8400</v>
       </c>
       <c r="X42" s="14" t="n">
         <f aca="false">J42-F42</f>
+        <v>-1600</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="22" t="n">
+        <v>25</v>
+      </c>
+      <c r="B43" s="23" t="s">
+        <v>169</v>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>5500</v>
+      </c>
+      <c r="D43" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="14" t="n">
+        <f aca="false">C43*D43</f>
+        <v>5500</v>
+      </c>
+      <c r="G43" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J43/GRANDCAR)</f>
+        <v>0.0154271780458503</v>
+      </c>
+      <c r="H43" s="14" t="n">
+        <f aca="false">J43/(1-MARGIN)</f>
+        <v>7500</v>
+      </c>
+      <c r="I43" s="14" t="n">
+        <f aca="false">H43-J43</f>
+        <v>3000</v>
+      </c>
+      <c r="J43" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L43),L43,IF(COUNT(O43,Q43,S43,U43)&gt;0,MIN(O43,Q43,S43,U43),F43))</f>
+        <v>4500</v>
+      </c>
+      <c r="K43" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L43),"Override",IF(COUNT(O43,Q43,S43,U43)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Low bid</v>
+      </c>
+      <c r="L43" s="10"/>
+      <c r="M43" s="14" t="n">
+        <f aca="false">IF(COUNT(O43,Q43,S43,U43)=0,"",MIN(O43,Q43,S43,U43))</f>
+        <v>4500</v>
+      </c>
+      <c r="N43" s="29" t="s">
+        <v>170</v>
+      </c>
+      <c r="O43" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="P43" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="Q43" s="27"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="27"/>
+      <c r="T43" s="6"/>
+      <c r="U43" s="27"/>
+      <c r="V43" s="8" t="s">
+        <v>172</v>
+      </c>
+      <c r="W43" s="14" t="n">
+        <f aca="false">IF(M43="",F43,M43)</f>
+        <v>4500</v>
+      </c>
+      <c r="X43" s="14" t="n">
+        <f aca="false">J43-F43</f>
+        <v>-1000</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="22" t="n">
+        <v>26</v>
+      </c>
+      <c r="B44" s="23" t="s">
+        <v>173</v>
+      </c>
+      <c r="C44" s="10" t="n">
+        <v>2000</v>
+      </c>
+      <c r="D44" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F44" s="14" t="n">
+        <f aca="false">C44*D44</f>
+        <v>2000</v>
+      </c>
+      <c r="G44" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J44/GRANDCAR)</f>
+        <v>0.00685652357593348</v>
+      </c>
+      <c r="H44" s="14" t="n">
+        <f aca="false">J44/(1-MARGIN)</f>
+        <v>3333.33333333333</v>
+      </c>
+      <c r="I44" s="14" t="n">
+        <f aca="false">H44-J44</f>
+        <v>1333.33333333333</v>
+      </c>
+      <c r="J44" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L44),L44,IF(COUNT(O44,Q44,S44,U44)&gt;0,MIN(O44,Q44,S44,U44),F44))</f>
+        <v>2000</v>
+      </c>
+      <c r="K44" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L44),"Override",IF(COUNT(O44,Q44,S44,U44)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L44" s="10"/>
+      <c r="M44" s="14" t="str">
+        <f aca="false">IF(COUNT(O44,Q44,S44,U44)=0,"",MIN(O44,Q44,S44,U44))</f>
+        <v/>
+      </c>
+      <c r="N44" s="6"/>
+      <c r="O44" s="27"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="27"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="27"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="27"/>
+      <c r="V44" s="8" t="s">
+        <v>174</v>
+      </c>
+      <c r="W44" s="14" t="n">
+        <f aca="false">IF(M44="",F44,M44)</f>
+        <v>2000</v>
+      </c>
+      <c r="X44" s="14" t="n">
+        <f aca="false">J44-F44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="22" t="n">
+        <v>27</v>
+      </c>
+      <c r="B45" s="23" t="s">
+        <v>175</v>
+      </c>
+      <c r="C45" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="D45" s="24" t="n">
+        <v>700</v>
+      </c>
+      <c r="E45" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F45" s="14" t="n">
+        <f aca="false">C45*D45</f>
+        <v>2100</v>
+      </c>
+      <c r="G45" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J45/GRANDCAR)</f>
+        <v>0.00801184779847827</v>
+      </c>
+      <c r="H45" s="14" t="n">
+        <f aca="false">J45/(1-MARGIN)</f>
+        <v>3895</v>
+      </c>
+      <c r="I45" s="14" t="n">
+        <f aca="false">H45-J45</f>
+        <v>1558</v>
+      </c>
+      <c r="J45" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L45),L45,IF(COUNT(O45,Q45,S45,U45)&gt;0,MIN(O45,Q45,S45,U45),F45))</f>
+        <v>2337</v>
+      </c>
+      <c r="K45" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L45),"Override",IF(COUNT(O45,Q45,S45,U45)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Low bid</v>
+      </c>
+      <c r="L45" s="10"/>
+      <c r="M45" s="14" t="n">
+        <f aca="false">IF(COUNT(O45,Q45,S45,U45)=0,"",MIN(O45,Q45,S45,U45))</f>
+        <v>2337</v>
+      </c>
+      <c r="N45" s="29" t="s">
+        <v>176</v>
+      </c>
+      <c r="O45" s="10" t="n">
+        <v>2337</v>
+      </c>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="27"/>
+      <c r="R45" s="6"/>
+      <c r="S45" s="27"/>
+      <c r="T45" s="6"/>
+      <c r="U45" s="27"/>
+      <c r="V45" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="W45" s="14" t="n">
+        <f aca="false">IF(M45="",F45,M45)</f>
+        <v>2337</v>
+      </c>
+      <c r="X45" s="14" t="n">
+        <f aca="false">J45-F45</f>
         <v>237</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="12" t="s">
-        <v>164</v>
-      </c>
-      <c r="F43" s="13" t="n">
-        <f aca="false">SUM(F39:F42)</f>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="F46" s="13" t="n">
+        <f aca="false">SUM(F42:F45)</f>
         <v>19600</v>
       </c>
-      <c r="G43" s="17" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J43/GRANDCAR)</f>
-        <v>0.0632798910662208</v>
-      </c>
-      <c r="H43" s="13" t="n">
-        <f aca="false">SUM(H39:H42)</f>
+      <c r="G46" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J46/GRANDCAR)</f>
+        <v>0.0590929484391827</v>
+      </c>
+      <c r="H46" s="13" t="n">
+        <f aca="false">SUM(H42:H45)</f>
         <v>28728.3333333333</v>
       </c>
-      <c r="I43" s="13" t="n">
-        <f aca="false">SUM(I39:I42)</f>
+      <c r="I46" s="13" t="n">
+        <f aca="false">SUM(I42:I45)</f>
         <v>11491.3333333333</v>
       </c>
-      <c r="J43" s="13" t="n">
-        <f aca="false">SUM(J39:J42)</f>
+      <c r="J46" s="13" t="n">
+        <f aca="false">SUM(J42:J45)</f>
         <v>17237</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20"/>
-      <c r="B45" s="21" t="s">
-        <v>165</v>
-      </c>
-      <c r="C45" s="20"/>
-      <c r="D45" s="20"/>
-      <c r="E45" s="20"/>
-      <c r="F45" s="20"/>
-      <c r="G45" s="20"/>
-      <c r="H45" s="20"/>
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="20"/>
-      <c r="N45" s="20"/>
-      <c r="O45" s="20"/>
-      <c r="P45" s="20"/>
-      <c r="Q45" s="20"/>
-      <c r="R45" s="20"/>
-      <c r="S45" s="20"/>
-      <c r="T45" s="20"/>
-      <c r="U45" s="20"/>
-      <c r="V45" s="20"/>
-    </row>
-    <row r="46" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="22" t="n">
-        <v>25</v>
-      </c>
-      <c r="B46" s="23" t="s">
-        <v>166</v>
-      </c>
-      <c r="C46" s="11" t="n">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="20"/>
+      <c r="B48" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="F48" s="20"/>
+      <c r="G48" s="20"/>
+      <c r="H48" s="20"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="20"/>
+      <c r="N48" s="20"/>
+      <c r="O48" s="20"/>
+      <c r="P48" s="20"/>
+      <c r="Q48" s="20"/>
+      <c r="R48" s="20"/>
+      <c r="S48" s="20"/>
+      <c r="T48" s="20"/>
+      <c r="U48" s="20"/>
+      <c r="V48" s="20"/>
+    </row>
+    <row r="49" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="22" t="n">
+        <v>28</v>
+      </c>
+      <c r="B49" s="23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C49" s="11" t="n">
         <f aca="false">FVBUILD</f>
         <v>53550.9</v>
       </c>
-      <c r="D46" s="24" t="n">
+      <c r="D49" s="24" t="n">
         <v>1</v>
       </c>
-      <c r="E46" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F46" s="14" t="n">
-        <f aca="false">C46*D46</f>
+      <c r="E49" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="14" t="n">
+        <f aca="false">C49*D49</f>
         <v>53550.9</v>
       </c>
-      <c r="G46" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J46/GRANDCAR)</f>
-        <v>0.137668730926686</v>
-      </c>
-      <c r="H46" s="14" t="n">
-        <f aca="false">J46/(1-MARGIN)</f>
+      <c r="G49" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J49/GRANDCAR)</f>
+        <v>0.128559817048753</v>
+      </c>
+      <c r="H49" s="14" t="n">
+        <f aca="false">J49/(1-MARGIN)</f>
         <v>62500</v>
       </c>
-      <c r="I46" s="14" t="n">
-        <f aca="false">H46-J46</f>
+      <c r="I49" s="14" t="n">
+        <f aca="false">H49-J49</f>
         <v>25000</v>
       </c>
-      <c r="J46" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L46),L46,IF(COUNT(O46,Q46,S46,U46)&gt;0,MIN(O46,Q46,S46,U46),F46))</f>
+      <c r="J49" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L49),L49,IF(COUNT(O49,Q49,S49,U49)&gt;0,MIN(O49,Q49,S49,U49),F49))</f>
         <v>37500</v>
       </c>
-      <c r="K46" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L46),"Override",IF(COUNT(O46,Q46,S46,U46)&gt;0,"Low bid","Internal rate"))</f>
+      <c r="K49" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L49),"Override",IF(COUNT(O49,Q49,S49,U49)&gt;0,"Low bid","Internal rate"))</f>
         <v>Override</v>
       </c>
-      <c r="L46" s="10" t="n">
+      <c r="L49" s="10" t="n">
         <v>37500</v>
       </c>
-      <c r="M46" s="14" t="n">
-        <f aca="false">IF(COUNT(O46,Q46,S46,U46)=0,"",MIN(O46,Q46,S46,U46))</f>
+      <c r="M49" s="14" t="n">
+        <f aca="false">IF(COUNT(O49,Q49,S49,U49)=0,"",MIN(O49,Q49,S49,U49))</f>
         <v>78000</v>
       </c>
-      <c r="N46" s="29" t="s">
-        <v>167</v>
-      </c>
-      <c r="O46" s="10" t="n">
+      <c r="N49" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="O49" s="10" t="n">
         <v>78000</v>
       </c>
-      <c r="P46" s="29" t="s">
-        <v>168</v>
-      </c>
-      <c r="Q46" s="10" t="n">
+      <c r="P49" s="29" t="s">
+        <v>182</v>
+      </c>
+      <c r="Q49" s="10" t="n">
         <v>109500</v>
       </c>
-      <c r="R46" s="6"/>
-      <c r="S46" s="27"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="27"/>
-      <c r="V46" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="W46" s="14" t="n">
-        <f aca="false">L46</f>
+      <c r="R49" s="6"/>
+      <c r="S49" s="27"/>
+      <c r="T49" s="6"/>
+      <c r="U49" s="27"/>
+      <c r="V49" s="8" t="s">
+        <v>183</v>
+      </c>
+      <c r="W49" s="14" t="n">
+        <f aca="false">L49</f>
         <v>37500</v>
       </c>
-      <c r="X46" s="14" t="n">
-        <f aca="false">J46-F46</f>
+      <c r="X49" s="14" t="n">
+        <f aca="false">J49-F49</f>
         <v>-16050.9</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="12" t="s">
-        <v>170</v>
-      </c>
-      <c r="F47" s="13" t="n">
-        <f aca="false">SUM(F46:F46)</f>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="F50" s="13" t="n">
+        <f aca="false">SUM(F49:F49)</f>
         <v>53550.9</v>
       </c>
-      <c r="G47" s="17" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J47/GRANDCAR)</f>
-        <v>0.137668730926686</v>
-      </c>
-      <c r="H47" s="13" t="n">
-        <f aca="false">SUM(H46:H46)</f>
+      <c r="G50" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J50/GRANDCAR)</f>
+        <v>0.128559817048753</v>
+      </c>
+      <c r="H50" s="13" t="n">
+        <f aca="false">SUM(H49:H49)</f>
         <v>62500</v>
       </c>
-      <c r="I47" s="13" t="n">
-        <f aca="false">SUM(I46:I46)</f>
+      <c r="I50" s="13" t="n">
+        <f aca="false">SUM(I49:I49)</f>
         <v>25000</v>
       </c>
-      <c r="J47" s="13" t="n">
-        <f aca="false">SUM(J46:J46)</f>
+      <c r="J50" s="13" t="n">
+        <f aca="false">SUM(J49:J49)</f>
         <v>37500</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20"/>
-      <c r="B49" s="21" t="s">
-        <v>171</v>
-      </c>
-      <c r="C49" s="20"/>
-      <c r="D49" s="20"/>
-      <c r="E49" s="20"/>
-      <c r="F49" s="20"/>
-      <c r="G49" s="20"/>
-      <c r="H49" s="20"/>
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="20"/>
-      <c r="N49" s="20"/>
-      <c r="O49" s="20"/>
-      <c r="P49" s="20"/>
-      <c r="Q49" s="20"/>
-      <c r="R49" s="20"/>
-      <c r="S49" s="20"/>
-      <c r="T49" s="20"/>
-      <c r="U49" s="20"/>
-      <c r="V49" s="20"/>
-    </row>
-    <row r="50" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="22" t="n">
-        <v>26</v>
-      </c>
-      <c r="B50" s="23" t="s">
-        <v>172</v>
-      </c>
-      <c r="C50" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D50" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F50" s="14" t="n">
-        <f aca="false">C50*D50</f>
-        <v>1200</v>
-      </c>
-      <c r="G50" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J50/GRANDCAR)</f>
-        <v>0.00440539938965394</v>
-      </c>
-      <c r="H50" s="14" t="n">
-        <f aca="false">J50/(1-MARGIN)</f>
-        <v>2000</v>
-      </c>
-      <c r="I50" s="14" t="n">
-        <f aca="false">H50-J50</f>
-        <v>800</v>
-      </c>
-      <c r="J50" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L50),L50,IF(COUNT(O50,Q50,S50,U50)&gt;0,MIN(O50,Q50,S50,U50),F50))</f>
-        <v>1200</v>
-      </c>
-      <c r="K50" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L50),"Override",IF(COUNT(O50,Q50,S50,U50)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Internal rate</v>
-      </c>
-      <c r="L50" s="10"/>
-      <c r="M50" s="14" t="str">
-        <f aca="false">IF(COUNT(O50,Q50,S50,U50)=0,"",MIN(O50,Q50,S50,U50))</f>
-        <v/>
-      </c>
-      <c r="N50" s="6"/>
-      <c r="O50" s="27"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="27"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="27"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="27"/>
-      <c r="V50" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="W50" s="14" t="n">
-        <f aca="false">IF(M50="",F50,M50)</f>
-        <v>1200</v>
-      </c>
-      <c r="X50" s="14" t="n">
-        <f aca="false">J50-F50</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="22" t="n">
-        <v>27</v>
-      </c>
-      <c r="B51" s="23" t="s">
-        <v>174</v>
-      </c>
-      <c r="C51" s="10" t="n">
-        <v>400</v>
-      </c>
-      <c r="D51" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F51" s="14" t="n">
-        <f aca="false">C51*D51</f>
-        <v>400</v>
-      </c>
-      <c r="G51" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J51/GRANDCAR)</f>
-        <v>0.00146846646321798</v>
-      </c>
-      <c r="H51" s="14" t="n">
-        <f aca="false">J51/(1-MARGIN)</f>
-        <v>666.666666666667</v>
-      </c>
-      <c r="I51" s="14" t="n">
-        <f aca="false">H51-J51</f>
-        <v>266.666666666667</v>
-      </c>
-      <c r="J51" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L51),L51,IF(COUNT(O51,Q51,S51,U51)&gt;0,MIN(O51,Q51,S51,U51),F51))</f>
-        <v>400</v>
-      </c>
-      <c r="K51" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L51),"Override",IF(COUNT(O51,Q51,S51,U51)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Internal rate</v>
-      </c>
-      <c r="L51" s="10"/>
-      <c r="M51" s="14" t="str">
-        <f aca="false">IF(COUNT(O51,Q51,S51,U51)=0,"",MIN(O51,Q51,S51,U51))</f>
-        <v/>
-      </c>
-      <c r="N51" s="6"/>
-      <c r="O51" s="27"/>
-      <c r="P51" s="6"/>
-      <c r="Q51" s="27"/>
-      <c r="R51" s="6"/>
-      <c r="S51" s="27"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="27"/>
-      <c r="V51" s="8" t="s">
-        <v>175</v>
-      </c>
-      <c r="W51" s="14" t="n">
-        <f aca="false">IF(M51="",F51,M51)</f>
-        <v>400</v>
-      </c>
-      <c r="X51" s="14" t="n">
-        <f aca="false">J51-F51</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="22" t="n">
-        <v>28</v>
-      </c>
-      <c r="B52" s="23" t="s">
-        <v>176</v>
-      </c>
-      <c r="C52" s="30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D52" s="24" t="n">
-        <v>600</v>
-      </c>
-      <c r="E52" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="F52" s="14" t="n">
-        <f aca="false">C52*D52</f>
-        <v>2700</v>
-      </c>
-      <c r="G52" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J52/GRANDCAR)</f>
-        <v>0.00826012385560114</v>
-      </c>
-      <c r="H52" s="14" t="n">
-        <f aca="false">J52/(1-MARGIN)</f>
-        <v>3750</v>
-      </c>
-      <c r="I52" s="14" t="n">
-        <f aca="false">H52-J52</f>
-        <v>1500</v>
-      </c>
-      <c r="J52" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L52),L52,IF(COUNT(O52,Q52,S52,U52)&gt;0,MIN(O52,Q52,S52,U52),F52))</f>
-        <v>2250</v>
-      </c>
-      <c r="K52" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L52),"Override",IF(COUNT(O52,Q52,S52,U52)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Low bid</v>
-      </c>
-      <c r="L52" s="10"/>
-      <c r="M52" s="14" t="n">
-        <f aca="false">IF(COUNT(O52,Q52,S52,U52)=0,"",MIN(O52,Q52,S52,U52))</f>
-        <v>2250</v>
-      </c>
-      <c r="N52" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="O52" s="10" t="n">
-        <v>2250</v>
-      </c>
-      <c r="P52" s="6"/>
-      <c r="Q52" s="27"/>
-      <c r="R52" s="6"/>
-      <c r="S52" s="27"/>
-      <c r="T52" s="6"/>
-      <c r="U52" s="27"/>
-      <c r="V52" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="W52" s="14" t="n">
-        <f aca="false">IF(M52="",F52,M52)</f>
-        <v>2250</v>
-      </c>
-      <c r="X52" s="14" t="n">
-        <f aca="false">J52-F52</f>
-        <v>-450</v>
-      </c>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="20"/>
+      <c r="B52" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="C52" s="20"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="20"/>
+      <c r="G52" s="20"/>
+      <c r="H52" s="20"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="20"/>
+      <c r="N52" s="20"/>
+      <c r="O52" s="20"/>
+      <c r="P52" s="20"/>
+      <c r="Q52" s="20"/>
+      <c r="R52" s="20"/>
+      <c r="S52" s="20"/>
+      <c r="T52" s="20"/>
+      <c r="U52" s="20"/>
+      <c r="V52" s="20"/>
     </row>
     <row r="53" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="22" t="n">
         <v>29</v>
       </c>
       <c r="B53" s="23" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C53" s="10" t="n">
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="D53" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E53" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F53" s="14" t="n">
         <f aca="false">C53*D53</f>
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="G53" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J53/GRANDCAR)</f>
-        <v>0.0183558307902248</v>
+        <v>0.00411391414556009</v>
       </c>
       <c r="H53" s="14" t="n">
         <f aca="false">J53/(1-MARGIN)</f>
-        <v>8333.33333333333</v>
+        <v>2000</v>
       </c>
       <c r="I53" s="14" t="n">
         <f aca="false">H53-J53</f>
-        <v>3333.33333333333</v>
+        <v>800</v>
       </c>
       <c r="J53" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L53),L53,IF(COUNT(O53,Q53,S53,U53)&gt;0,MIN(O53,Q53,S53,U53),F53))</f>
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="K53" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L53),"Override",IF(COUNT(O53,Q53,S53,U53)&gt;0,"Low bid","Internal rate"))</f>
@@ -4452,68 +4599,64 @@
       <c r="T53" s="6"/>
       <c r="U53" s="27"/>
       <c r="V53" s="8" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="W53" s="14" t="n">
         <f aca="false">IF(M53="",F53,M53)</f>
-        <v>5000</v>
+        <v>1200</v>
       </c>
       <c r="X53" s="14" t="n">
         <f aca="false">J53-F53</f>
         <v>0</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="22" t="n">
         <v>30</v>
       </c>
       <c r="B54" s="23" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C54" s="10" t="n">
-        <v>4500</v>
+        <v>400</v>
       </c>
       <c r="D54" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E54" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F54" s="14" t="n">
         <f aca="false">C54*D54</f>
-        <v>4500</v>
+        <v>400</v>
       </c>
       <c r="G54" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J54/GRANDCAR)</f>
-        <v>0.0233853284267463</v>
+        <v>0.0013713047151867</v>
       </c>
       <c r="H54" s="14" t="n">
         <f aca="false">J54/(1-MARGIN)</f>
-        <v>10616.6666666667</v>
+        <v>666.666666666667</v>
       </c>
       <c r="I54" s="14" t="n">
         <f aca="false">H54-J54</f>
-        <v>4246.66666666667</v>
+        <v>266.666666666667</v>
       </c>
       <c r="J54" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L54),L54,IF(COUNT(O54,Q54,S54,U54)&gt;0,MIN(O54,Q54,S54,U54),F54))</f>
-        <v>6370</v>
+        <v>400</v>
       </c>
       <c r="K54" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L54),"Override",IF(COUNT(O54,Q54,S54,U54)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Low bid</v>
+        <v>Internal rate</v>
       </c>
       <c r="L54" s="10"/>
-      <c r="M54" s="14" t="n">
+      <c r="M54" s="14" t="str">
         <f aca="false">IF(COUNT(O54,Q54,S54,U54)=0,"",MIN(O54,Q54,S54,U54))</f>
-        <v>6370</v>
-      </c>
-      <c r="N54" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="O54" s="10" t="n">
-        <v>6370</v>
-      </c>
+        <v/>
+      </c>
+      <c r="N54" s="6"/>
+      <c r="O54" s="27"/>
       <c r="P54" s="6"/>
       <c r="Q54" s="27"/>
       <c r="R54" s="6"/>
@@ -4521,15 +4664,15 @@
       <c r="T54" s="6"/>
       <c r="U54" s="27"/>
       <c r="V54" s="8" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="W54" s="14" t="n">
         <f aca="false">IF(M54="",F54,M54)</f>
-        <v>6370</v>
+        <v>400</v>
       </c>
       <c r="X54" s="14" t="n">
         <f aca="false">J54-F54</f>
-        <v>1870</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4537,48 +4680,52 @@
         <v>31</v>
       </c>
       <c r="B55" s="23" t="s">
-        <v>184</v>
-      </c>
-      <c r="C55" s="10" t="n">
-        <v>130</v>
+        <v>190</v>
+      </c>
+      <c r="C55" s="30" t="n">
+        <v>4.5</v>
       </c>
       <c r="D55" s="24" t="n">
-        <v>5</v>
+        <v>600</v>
       </c>
       <c r="E55" s="22" t="s">
-        <v>109</v>
+        <v>129</v>
       </c>
       <c r="F55" s="14" t="n">
         <f aca="false">C55*D55</f>
-        <v>650</v>
+        <v>2700</v>
       </c>
       <c r="G55" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J55/GRANDCAR)</f>
-        <v>0.00238625800272922</v>
+        <v>0.00771358902292516</v>
       </c>
       <c r="H55" s="14" t="n">
         <f aca="false">J55/(1-MARGIN)</f>
-        <v>1083.33333333333</v>
+        <v>3750</v>
       </c>
       <c r="I55" s="14" t="n">
         <f aca="false">H55-J55</f>
-        <v>433.333333333334</v>
+        <v>1500</v>
       </c>
       <c r="J55" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L55),L55,IF(COUNT(O55,Q55,S55,U55)&gt;0,MIN(O55,Q55,S55,U55),F55))</f>
-        <v>650</v>
+        <v>2250</v>
       </c>
       <c r="K55" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L55),"Override",IF(COUNT(O55,Q55,S55,U55)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Internal rate</v>
+        <v>Low bid</v>
       </c>
       <c r="L55" s="10"/>
-      <c r="M55" s="14" t="str">
+      <c r="M55" s="14" t="n">
         <f aca="false">IF(COUNT(O55,Q55,S55,U55)=0,"",MIN(O55,Q55,S55,U55))</f>
-        <v/>
-      </c>
-      <c r="N55" s="6"/>
-      <c r="O55" s="27"/>
+        <v>2250</v>
+      </c>
+      <c r="N55" s="29" t="s">
+        <v>191</v>
+      </c>
+      <c r="O55" s="10" t="n">
+        <v>2250</v>
+      </c>
       <c r="P55" s="6"/>
       <c r="Q55" s="27"/>
       <c r="R55" s="6"/>
@@ -4586,15 +4733,15 @@
       <c r="T55" s="6"/>
       <c r="U55" s="27"/>
       <c r="V55" s="8" t="s">
-        <v>84</v>
+        <v>192</v>
       </c>
       <c r="W55" s="14" t="n">
         <f aca="false">IF(M55="",F55,M55)</f>
-        <v>650</v>
+        <v>2250</v>
       </c>
       <c r="X55" s="14" t="n">
         <f aca="false">J55-F55</f>
-        <v>0</v>
+        <v>-450</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4602,36 +4749,36 @@
         <v>32</v>
       </c>
       <c r="B56" s="23" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="C56" s="10" t="n">
-        <v>800</v>
+        <v>5000</v>
       </c>
       <c r="D56" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E56" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F56" s="14" t="n">
         <f aca="false">C56*D56</f>
-        <v>800</v>
+        <v>5000</v>
       </c>
       <c r="G56" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J56/GRANDCAR)</f>
-        <v>0.00293693292643596</v>
+        <v>0.0171413089398337</v>
       </c>
       <c r="H56" s="14" t="n">
         <f aca="false">J56/(1-MARGIN)</f>
-        <v>1333.33333333333</v>
+        <v>8333.33333333333</v>
       </c>
       <c r="I56" s="14" t="n">
         <f aca="false">H56-J56</f>
-        <v>533.333333333334</v>
+        <v>3333.33333333333</v>
       </c>
       <c r="J56" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L56),L56,IF(COUNT(O56,Q56,S56,U56)&gt;0,MIN(O56,Q56,S56,U56),F56))</f>
-        <v>800</v>
+        <v>5000</v>
       </c>
       <c r="K56" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L56),"Override",IF(COUNT(O56,Q56,S56,U56)&gt;0,"Low bid","Internal rate"))</f>
@@ -4651,298 +4798,302 @@
       <c r="T56" s="6"/>
       <c r="U56" s="27"/>
       <c r="V56" s="8" t="s">
-        <v>96</v>
+        <v>194</v>
       </c>
       <c r="W56" s="14" t="n">
         <f aca="false">IF(M56="",F56,M56)</f>
-        <v>800</v>
+        <v>5000</v>
       </c>
       <c r="X56" s="14" t="n">
         <f aca="false">J56-F56</f>
         <v>0</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="12" t="s">
-        <v>186</v>
-      </c>
-      <c r="F57" s="13" t="n">
-        <f aca="false">SUM(F50:F56)</f>
+    <row r="57" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="22" t="n">
+        <v>33</v>
+      </c>
+      <c r="B57" s="23" t="s">
+        <v>195</v>
+      </c>
+      <c r="C57" s="10" t="n">
+        <v>4500</v>
+      </c>
+      <c r="D57" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E57" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F57" s="14" t="n">
+        <f aca="false">C57*D57</f>
+        <v>4500</v>
+      </c>
+      <c r="G57" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J57/GRANDCAR)</f>
+        <v>0.0218380275893481</v>
+      </c>
+      <c r="H57" s="14" t="n">
+        <f aca="false">J57/(1-MARGIN)</f>
+        <v>10616.6666666667</v>
+      </c>
+      <c r="I57" s="14" t="n">
+        <f aca="false">H57-J57</f>
+        <v>4246.66666666667</v>
+      </c>
+      <c r="J57" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L57),L57,IF(COUNT(O57,Q57,S57,U57)&gt;0,MIN(O57,Q57,S57,U57),F57))</f>
+        <v>6370</v>
+      </c>
+      <c r="K57" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L57),"Override",IF(COUNT(O57,Q57,S57,U57)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Low bid</v>
+      </c>
+      <c r="L57" s="10"/>
+      <c r="M57" s="14" t="n">
+        <f aca="false">IF(COUNT(O57,Q57,S57,U57)=0,"",MIN(O57,Q57,S57,U57))</f>
+        <v>6370</v>
+      </c>
+      <c r="N57" s="29" t="s">
+        <v>196</v>
+      </c>
+      <c r="O57" s="10" t="n">
+        <v>6370</v>
+      </c>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="27"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="27"/>
+      <c r="T57" s="6"/>
+      <c r="U57" s="27"/>
+      <c r="V57" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="W57" s="14" t="n">
+        <f aca="false">IF(M57="",F57,M57)</f>
+        <v>6370</v>
+      </c>
+      <c r="X57" s="14" t="n">
+        <f aca="false">J57-F57</f>
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="22" t="n">
+        <v>34</v>
+      </c>
+      <c r="B58" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <v>130</v>
+      </c>
+      <c r="D58" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E58" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="F58" s="14" t="n">
+        <f aca="false">C58*D58</f>
+        <v>650</v>
+      </c>
+      <c r="G58" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J58/GRANDCAR)</f>
+        <v>0.00222837016217838</v>
+      </c>
+      <c r="H58" s="14" t="n">
+        <f aca="false">J58/(1-MARGIN)</f>
+        <v>1083.33333333333</v>
+      </c>
+      <c r="I58" s="14" t="n">
+        <f aca="false">H58-J58</f>
+        <v>433.333333333334</v>
+      </c>
+      <c r="J58" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L58),L58,IF(COUNT(O58,Q58,S58,U58)&gt;0,MIN(O58,Q58,S58,U58),F58))</f>
+        <v>650</v>
+      </c>
+      <c r="K58" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L58),"Override",IF(COUNT(O58,Q58,S58,U58)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L58" s="10"/>
+      <c r="M58" s="14" t="str">
+        <f aca="false">IF(COUNT(O58,Q58,S58,U58)=0,"",MIN(O58,Q58,S58,U58))</f>
+        <v/>
+      </c>
+      <c r="N58" s="6"/>
+      <c r="O58" s="27"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="27"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="27"/>
+      <c r="T58" s="6"/>
+      <c r="U58" s="27"/>
+      <c r="V58" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="W58" s="14" t="n">
+        <f aca="false">IF(M58="",F58,M58)</f>
+        <v>650</v>
+      </c>
+      <c r="X58" s="14" t="n">
+        <f aca="false">J58-F58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="22" t="n">
+        <v>35</v>
+      </c>
+      <c r="B59" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <v>800</v>
+      </c>
+      <c r="D59" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E59" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F59" s="14" t="n">
+        <f aca="false">C59*D59</f>
+        <v>800</v>
+      </c>
+      <c r="G59" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J59/GRANDCAR)</f>
+        <v>0.00274260943037339</v>
+      </c>
+      <c r="H59" s="14" t="n">
+        <f aca="false">J59/(1-MARGIN)</f>
+        <v>1333.33333333333</v>
+      </c>
+      <c r="I59" s="14" t="n">
+        <f aca="false">H59-J59</f>
+        <v>533.333333333334</v>
+      </c>
+      <c r="J59" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L59),L59,IF(COUNT(O59,Q59,S59,U59)&gt;0,MIN(O59,Q59,S59,U59),F59))</f>
+        <v>800</v>
+      </c>
+      <c r="K59" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L59),"Override",IF(COUNT(O59,Q59,S59,U59)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L59" s="10"/>
+      <c r="M59" s="14" t="str">
+        <f aca="false">IF(COUNT(O59,Q59,S59,U59)=0,"",MIN(O59,Q59,S59,U59))</f>
+        <v/>
+      </c>
+      <c r="N59" s="6"/>
+      <c r="O59" s="27"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="27"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="27"/>
+      <c r="T59" s="6"/>
+      <c r="U59" s="27"/>
+      <c r="V59" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="W59" s="14" t="n">
+        <f aca="false">IF(M59="",F59,M59)</f>
+        <v>800</v>
+      </c>
+      <c r="X59" s="14" t="n">
+        <f aca="false">J59-F59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F60" s="13" t="n">
+        <f aca="false">SUM(F53:F59)</f>
         <v>15250</v>
       </c>
-      <c r="G57" s="17" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J57/GRANDCAR)</f>
-        <v>0.0611983398546093</v>
-      </c>
-      <c r="H57" s="13" t="n">
-        <f aca="false">SUM(H50:H56)</f>
+      <c r="G60" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J60/GRANDCAR)</f>
+        <v>0.0571491240054056</v>
+      </c>
+      <c r="H60" s="13" t="n">
+        <f aca="false">SUM(H53:H59)</f>
         <v>27783.3333333333</v>
       </c>
-      <c r="I57" s="13" t="n">
-        <f aca="false">SUM(I50:I56)</f>
+      <c r="I60" s="13" t="n">
+        <f aca="false">SUM(I53:I59)</f>
         <v>11113.3333333333</v>
       </c>
-      <c r="J57" s="13" t="n">
-        <f aca="false">SUM(J50:J56)</f>
+      <c r="J60" s="13" t="n">
+        <f aca="false">SUM(J53:J59)</f>
         <v>16670</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="20"/>
-      <c r="B59" s="21" t="s">
-        <v>187</v>
-      </c>
-      <c r="C59" s="20"/>
-      <c r="D59" s="20"/>
-      <c r="E59" s="20"/>
-      <c r="F59" s="20"/>
-      <c r="G59" s="20"/>
-      <c r="H59" s="20"/>
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="20"/>
-      <c r="N59" s="20"/>
-      <c r="O59" s="20"/>
-      <c r="P59" s="20"/>
-      <c r="Q59" s="20"/>
-      <c r="R59" s="20"/>
-      <c r="S59" s="20"/>
-      <c r="T59" s="20"/>
-      <c r="U59" s="20"/>
-      <c r="V59" s="20"/>
-    </row>
-    <row r="60" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="22" t="n">
-        <v>33</v>
-      </c>
-      <c r="B60" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="C60" s="10" t="n">
-        <v>1200</v>
-      </c>
-      <c r="D60" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F60" s="14" t="n">
-        <f aca="false">C60*D60</f>
-        <v>1200</v>
-      </c>
-      <c r="G60" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J60/GRANDCAR)</f>
-        <v>0.00440539938965394</v>
-      </c>
-      <c r="H60" s="14" t="n">
-        <f aca="false">J60/(1-MARGIN)</f>
-        <v>2000</v>
-      </c>
-      <c r="I60" s="14" t="n">
-        <f aca="false">H60-J60</f>
-        <v>800</v>
-      </c>
-      <c r="J60" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L60),L60,IF(COUNT(O60,Q60,S60,U60)&gt;0,MIN(O60,Q60,S60,U60),F60))</f>
-        <v>1200</v>
-      </c>
-      <c r="K60" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L60),"Override",IF(COUNT(O60,Q60,S60,U60)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Internal rate</v>
-      </c>
-      <c r="L60" s="10"/>
-      <c r="M60" s="14" t="str">
-        <f aca="false">IF(COUNT(O60,Q60,S60,U60)=0,"",MIN(O60,Q60,S60,U60))</f>
-        <v/>
-      </c>
-      <c r="N60" s="6"/>
-      <c r="O60" s="27"/>
-      <c r="P60" s="6"/>
-      <c r="Q60" s="27"/>
-      <c r="R60" s="6"/>
-      <c r="S60" s="27"/>
-      <c r="T60" s="6"/>
-      <c r="U60" s="27"/>
-      <c r="V60" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="W60" s="14" t="n">
-        <f aca="false">IF(M60="",F60,M60)</f>
-        <v>1200</v>
-      </c>
-      <c r="X60" s="14" t="n">
-        <f aca="false">J60-F60</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="22" t="n">
-        <v>34</v>
-      </c>
-      <c r="B61" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="C61" s="10" t="n">
-        <v>3000</v>
-      </c>
-      <c r="D61" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F61" s="14" t="n">
-        <f aca="false">C61*D61</f>
-        <v>3000</v>
-      </c>
-      <c r="G61" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J61/GRANDCAR)</f>
-        <v>0.0110134984741349</v>
-      </c>
-      <c r="H61" s="14" t="n">
-        <f aca="false">J61/(1-MARGIN)</f>
-        <v>5000</v>
-      </c>
-      <c r="I61" s="14" t="n">
-        <f aca="false">H61-J61</f>
-        <v>2000</v>
-      </c>
-      <c r="J61" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L61),L61,IF(COUNT(O61,Q61,S61,U61)&gt;0,MIN(O61,Q61,S61,U61),F61))</f>
-        <v>3000</v>
-      </c>
-      <c r="K61" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L61),"Override",IF(COUNT(O61,Q61,S61,U61)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Internal rate</v>
-      </c>
-      <c r="L61" s="10"/>
-      <c r="M61" s="14" t="str">
-        <f aca="false">IF(COUNT(O61,Q61,S61,U61)=0,"",MIN(O61,Q61,S61,U61))</f>
-        <v/>
-      </c>
-      <c r="N61" s="6"/>
-      <c r="O61" s="27"/>
-      <c r="P61" s="6"/>
-      <c r="Q61" s="27"/>
-      <c r="R61" s="6"/>
-      <c r="S61" s="27"/>
-      <c r="T61" s="6"/>
-      <c r="U61" s="27"/>
-      <c r="V61" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="W61" s="14" t="n">
-        <f aca="false">IF(M61="",F61,M61)</f>
-        <v>3000</v>
-      </c>
-      <c r="X61" s="14" t="n">
-        <f aca="false">J61-F61</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="22" t="n">
-        <v>35</v>
-      </c>
-      <c r="B62" s="23" t="s">
-        <v>191</v>
-      </c>
-      <c r="C62" s="10" t="n">
-        <v>800</v>
-      </c>
-      <c r="D62" s="24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" s="22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F62" s="14" t="n">
-        <f aca="false">C62*D62</f>
-        <v>800</v>
-      </c>
-      <c r="G62" s="16" t="n">
-        <f aca="false">IF(GRANDCAR=0,0,J62/GRANDCAR)</f>
-        <v>0.00293693292643596</v>
-      </c>
-      <c r="H62" s="14" t="n">
-        <f aca="false">J62/(1-MARGIN)</f>
-        <v>1333.33333333333</v>
-      </c>
-      <c r="I62" s="14" t="n">
-        <f aca="false">H62-J62</f>
-        <v>533.333333333334</v>
-      </c>
-      <c r="J62" s="25" t="n">
-        <f aca="false">IF(ISNUMBER(L62),L62,IF(COUNT(O62,Q62,S62,U62)&gt;0,MIN(O62,Q62,S62,U62),F62))</f>
-        <v>800</v>
-      </c>
-      <c r="K62" s="26" t="str">
-        <f aca="false">IF(ISNUMBER(L62),"Override",IF(COUNT(O62,Q62,S62,U62)&gt;0,"Low bid","Internal rate"))</f>
-        <v>Internal rate</v>
-      </c>
-      <c r="L62" s="10"/>
-      <c r="M62" s="14" t="str">
-        <f aca="false">IF(COUNT(O62,Q62,S62,U62)=0,"",MIN(O62,Q62,S62,U62))</f>
-        <v/>
-      </c>
-      <c r="N62" s="6"/>
-      <c r="O62" s="27"/>
-      <c r="P62" s="6"/>
-      <c r="Q62" s="27"/>
-      <c r="R62" s="6"/>
-      <c r="S62" s="27"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="27"/>
-      <c r="V62" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="W62" s="14" t="n">
-        <f aca="false">IF(M62="",F62,M62)</f>
-        <v>800</v>
-      </c>
-      <c r="X62" s="14" t="n">
-        <f aca="false">J62-F62</f>
-        <v>0</v>
-      </c>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="20"/>
+      <c r="B62" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="C62" s="20"/>
+      <c r="D62" s="20"/>
+      <c r="E62" s="20"/>
+      <c r="F62" s="20"/>
+      <c r="G62" s="20"/>
+      <c r="H62" s="20"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="20"/>
+      <c r="N62" s="20"/>
+      <c r="O62" s="20"/>
+      <c r="P62" s="20"/>
+      <c r="Q62" s="20"/>
+      <c r="R62" s="20"/>
+      <c r="S62" s="20"/>
+      <c r="T62" s="20"/>
+      <c r="U62" s="20"/>
+      <c r="V62" s="20"/>
     </row>
     <row r="63" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="22" t="n">
         <v>36</v>
       </c>
       <c r="B63" s="23" t="s">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="C63" s="10" t="n">
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="D63" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E63" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F63" s="14" t="n">
         <f aca="false">C63*D63</f>
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="G63" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J63/GRANDCAR)</f>
-        <v>0.00550674923706743</v>
+        <v>0.00411391414556009</v>
       </c>
       <c r="H63" s="14" t="n">
         <f aca="false">J63/(1-MARGIN)</f>
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="I63" s="14" t="n">
         <f aca="false">H63-J63</f>
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="J63" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L63),L63,IF(COUNT(O63,Q63,S63,U63)&gt;0,MIN(O63,Q63,S63,U63),F63))</f>
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="K63" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L63),"Override",IF(COUNT(O63,Q63,S63,U63)&gt;0,"Low bid","Internal rate"))</f>
@@ -4962,52 +5113,52 @@
       <c r="T63" s="6"/>
       <c r="U63" s="27"/>
       <c r="V63" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="W63" s="14" t="n">
         <f aca="false">IF(M63="",F63,M63)</f>
-        <v>1500</v>
+        <v>1200</v>
       </c>
       <c r="X63" s="14" t="n">
         <f aca="false">J63-F63</f>
         <v>0</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="22" t="n">
         <v>37</v>
       </c>
       <c r="B64" s="23" t="s">
-        <v>193</v>
+        <v>203</v>
       </c>
       <c r="C64" s="10" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="D64" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E64" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F64" s="14" t="n">
         <f aca="false">C64*D64</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G64" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J64/GRANDCAR)</f>
-        <v>0.00367116615804495</v>
+        <v>0.00514239268195011</v>
       </c>
       <c r="H64" s="14" t="n">
         <f aca="false">J64/(1-MARGIN)</f>
-        <v>1666.66666666667</v>
+        <v>2500</v>
       </c>
       <c r="I64" s="14" t="n">
         <f aca="false">H64-J64</f>
-        <v>666.666666666667</v>
+        <v>1000</v>
       </c>
       <c r="J64" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L64),L64,IF(COUNT(O64,Q64,S64,U64)&gt;0,MIN(O64,Q64,S64,U64),F64))</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="K64" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L64),"Override",IF(COUNT(O64,Q64,S64,U64)&gt;0,"Low bid","Internal rate"))</f>
@@ -5027,11 +5178,11 @@
       <c r="T64" s="6"/>
       <c r="U64" s="27"/>
       <c r="V64" s="8" t="s">
-        <v>96</v>
+        <v>204</v>
       </c>
       <c r="W64" s="14" t="n">
         <f aca="false">IF(M64="",F64,M64)</f>
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="X64" s="14" t="n">
         <f aca="false">J64-F64</f>
@@ -5043,36 +5194,36 @@
         <v>38</v>
       </c>
       <c r="B65" s="23" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C65" s="10" t="n">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="D65" s="24" t="n">
         <v>1</v>
       </c>
       <c r="E65" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F65" s="14" t="n">
         <f aca="false">C65*D65</f>
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="G65" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J65/GRANDCAR)</f>
-        <v>0.00256981631063147</v>
+        <v>0.00274260943037339</v>
       </c>
       <c r="H65" s="14" t="n">
         <f aca="false">J65/(1-MARGIN)</f>
-        <v>1166.66666666667</v>
+        <v>1333.33333333333</v>
       </c>
       <c r="I65" s="14" t="n">
         <f aca="false">H65-J65</f>
-        <v>466.666666666667</v>
+        <v>533.333333333334</v>
       </c>
       <c r="J65" s="25" t="n">
         <f aca="false">IF(ISNUMBER(L65),L65,IF(COUNT(O65,Q65,S65,U65)&gt;0,MIN(O65,Q65,S65,U65),F65))</f>
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="K65" s="26" t="str">
         <f aca="false">IF(ISNUMBER(L65),"Override",IF(COUNT(O65,Q65,S65,U65)&gt;0,"Low bid","Internal rate"))</f>
@@ -5092,76 +5243,336 @@
       <c r="T65" s="6"/>
       <c r="U65" s="27"/>
       <c r="V65" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="W65" s="14" t="n">
         <f aca="false">IF(M65="",F65,M65)</f>
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="X65" s="14" t="n">
         <f aca="false">J65-F65</f>
         <v>0</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="12" t="s">
-        <v>195</v>
-      </c>
-      <c r="F66" s="13" t="n">
-        <f aca="false">SUM(F60:F65)</f>
-        <v>8200</v>
-      </c>
-      <c r="G66" s="17" t="n">
+    <row r="66" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="22" t="n">
+        <v>39</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="C66" s="10" t="n">
+        <v>1500</v>
+      </c>
+      <c r="D66" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F66" s="14" t="n">
+        <f aca="false">C66*D66</f>
+        <v>1500</v>
+      </c>
+      <c r="G66" s="16" t="n">
         <f aca="false">IF(GRANDCAR=0,0,J66/GRANDCAR)</f>
-        <v>0.0301035624959686</v>
-      </c>
-      <c r="H66" s="13" t="n">
-        <f aca="false">SUM(H60:H65)</f>
-        <v>13666.6666666667</v>
-      </c>
-      <c r="I66" s="13" t="n">
-        <f aca="false">SUM(I60:I65)</f>
-        <v>5466.66666666667</v>
-      </c>
-      <c r="J66" s="13" t="n">
-        <f aca="false">SUM(J60:J65)</f>
-        <v>8200</v>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="31" t="s">
-        <v>196</v>
-      </c>
-      <c r="F68" s="32" t="n">
-        <f aca="false">F18+F24+F29+F36+F43+F47+F57+F66</f>
-        <v>289498.9</v>
-      </c>
-      <c r="G68" s="33" t="n">
+        <v>0.00514239268195011</v>
+      </c>
+      <c r="H66" s="14" t="n">
+        <f aca="false">J66/(1-MARGIN)</f>
+        <v>2500</v>
+      </c>
+      <c r="I66" s="14" t="n">
+        <f aca="false">H66-J66</f>
+        <v>1000</v>
+      </c>
+      <c r="J66" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L66),L66,IF(COUNT(O66,Q66,S66,U66)&gt;0,MIN(O66,Q66,S66,U66),F66))</f>
+        <v>1500</v>
+      </c>
+      <c r="K66" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L66),"Override",IF(COUNT(O66,Q66,S66,U66)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L66" s="10"/>
+      <c r="M66" s="14" t="str">
+        <f aca="false">IF(COUNT(O66,Q66,S66,U66)=0,"",MIN(O66,Q66,S66,U66))</f>
+        <v/>
+      </c>
+      <c r="N66" s="6"/>
+      <c r="O66" s="27"/>
+      <c r="P66" s="6"/>
+      <c r="Q66" s="27"/>
+      <c r="R66" s="6"/>
+      <c r="S66" s="27"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="27"/>
+      <c r="V66" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="W66" s="14" t="n">
+        <f aca="false">IF(M66="",F66,M66)</f>
+        <v>1500</v>
+      </c>
+      <c r="X66" s="14" t="n">
+        <f aca="false">J66-F66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="22" t="n">
+        <v>40</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>207</v>
+      </c>
+      <c r="C67" s="10" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D67" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F67" s="14" t="n">
+        <f aca="false">C67*D67</f>
+        <v>1000</v>
+      </c>
+      <c r="G67" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J67/GRANDCAR)</f>
+        <v>0.00342826178796674</v>
+      </c>
+      <c r="H67" s="14" t="n">
+        <f aca="false">J67/(1-MARGIN)</f>
+        <v>1666.66666666667</v>
+      </c>
+      <c r="I67" s="14" t="n">
+        <f aca="false">H67-J67</f>
+        <v>666.666666666667</v>
+      </c>
+      <c r="J67" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L67),L67,IF(COUNT(O67,Q67,S67,U67)&gt;0,MIN(O67,Q67,S67,U67),F67))</f>
+        <v>1000</v>
+      </c>
+      <c r="K67" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L67),"Override",IF(COUNT(O67,Q67,S67,U67)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L67" s="10"/>
+      <c r="M67" s="14" t="str">
+        <f aca="false">IF(COUNT(O67,Q67,S67,U67)=0,"",MIN(O67,Q67,S67,U67))</f>
+        <v/>
+      </c>
+      <c r="N67" s="6"/>
+      <c r="O67" s="27"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="27"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="27"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="27"/>
+      <c r="V67" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="W67" s="14" t="n">
+        <f aca="false">IF(M67="",F67,M67)</f>
+        <v>1000</v>
+      </c>
+      <c r="X67" s="14" t="n">
+        <f aca="false">J67-F67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="36" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="22" t="n">
+        <v>41</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="C68" s="30" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="D68" s="24" t="n">
+        <v>400</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F68" s="14" t="n">
+        <f aca="false">C68*D68</f>
+        <v>3500</v>
+      </c>
+      <c r="G68" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J68/GRANDCAR)</f>
+        <v>0.0119989162578836</v>
+      </c>
+      <c r="H68" s="14" t="n">
+        <f aca="false">J68/(1-MARGIN)</f>
+        <v>5833.33333333333</v>
+      </c>
+      <c r="I68" s="14" t="n">
+        <f aca="false">H68-J68</f>
+        <v>2333.33333333333</v>
+      </c>
+      <c r="J68" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L68),L68,IF(COUNT(O68,Q68,S68,U68)&gt;0,MIN(O68,Q68,S68,U68),F68))</f>
+        <v>3500</v>
+      </c>
+      <c r="K68" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L68),"Override",IF(COUNT(O68,Q68,S68,U68)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L68" s="10"/>
+      <c r="M68" s="14" t="str">
+        <f aca="false">IF(COUNT(O68,Q68,S68,U68)=0,"",MIN(O68,Q68,S68,U68))</f>
+        <v/>
+      </c>
+      <c r="N68" s="6"/>
+      <c r="O68" s="27"/>
+      <c r="P68" s="6"/>
+      <c r="Q68" s="27"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="27"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="27"/>
+      <c r="V68" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="W68" s="14" t="n">
+        <f aca="false">IF(M68="",F68,M68)</f>
+        <v>3500</v>
+      </c>
+      <c r="X68" s="14" t="n">
+        <f aca="false">J68-F68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="22" t="n">
+        <v>42</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="C69" s="10" t="n">
+        <v>700</v>
+      </c>
+      <c r="D69" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="22" t="s">
+        <v>91</v>
+      </c>
+      <c r="F69" s="14" t="n">
+        <f aca="false">C69*D69</f>
+        <v>700</v>
+      </c>
+      <c r="G69" s="16" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J69/GRANDCAR)</f>
+        <v>0.00239978325157672</v>
+      </c>
+      <c r="H69" s="14" t="n">
+        <f aca="false">J69/(1-MARGIN)</f>
+        <v>1166.66666666667</v>
+      </c>
+      <c r="I69" s="14" t="n">
+        <f aca="false">H69-J69</f>
+        <v>466.666666666667</v>
+      </c>
+      <c r="J69" s="25" t="n">
+        <f aca="false">IF(ISNUMBER(L69),L69,IF(COUNT(O69,Q69,S69,U69)&gt;0,MIN(O69,Q69,S69,U69),F69))</f>
+        <v>700</v>
+      </c>
+      <c r="K69" s="26" t="str">
+        <f aca="false">IF(ISNUMBER(L69),"Override",IF(COUNT(O69,Q69,S69,U69)&gt;0,"Low bid","Internal rate"))</f>
+        <v>Internal rate</v>
+      </c>
+      <c r="L69" s="10"/>
+      <c r="M69" s="14" t="str">
+        <f aca="false">IF(COUNT(O69,Q69,S69,U69)=0,"",MIN(O69,Q69,S69,U69))</f>
+        <v/>
+      </c>
+      <c r="N69" s="6"/>
+      <c r="O69" s="27"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="27"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="27"/>
+      <c r="T69" s="6"/>
+      <c r="U69" s="27"/>
+      <c r="V69" s="8" t="s">
+        <v>104</v>
+      </c>
+      <c r="W69" s="14" t="n">
+        <f aca="false">IF(M69="",F69,M69)</f>
+        <v>700</v>
+      </c>
+      <c r="X69" s="14" t="n">
+        <f aca="false">J69-F69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F70" s="13" t="n">
+        <f aca="false">SUM(F63:F69)</f>
+        <v>10200</v>
+      </c>
+      <c r="G70" s="17" t="n">
+        <f aca="false">IF(GRANDCAR=0,0,J70/GRANDCAR)</f>
+        <v>0.0349682702372607</v>
+      </c>
+      <c r="H70" s="13" t="n">
+        <f aca="false">SUM(H63:H69)</f>
+        <v>17000</v>
+      </c>
+      <c r="I70" s="13" t="n">
+        <f aca="false">SUM(I63:I69)</f>
+        <v>6800</v>
+      </c>
+      <c r="J70" s="13" t="n">
+        <f aca="false">SUM(J63:J69)</f>
+        <v>10200</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="31" t="s">
+        <v>213</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <f aca="false">F21+F27+F32+F39+F46+F50+F60+F70</f>
+        <v>308798.9</v>
+      </c>
+      <c r="G72" s="33" t="n">
         <f aca="false">1</f>
         <v>1</v>
       </c>
-      <c r="H68" s="32" t="n">
-        <f aca="false">H18+H24+H29+H36+H43+H47+H57+H66</f>
-        <v>453988.35</v>
-      </c>
-      <c r="I68" s="32" t="n">
-        <f aca="false">I18+I24+I29+I36+I43+I47+I57+I66</f>
-        <v>181595.34</v>
-      </c>
-      <c r="J68" s="32" t="n">
-        <f aca="false">J18+J24+J29+J36+J43+J47+J57+J66</f>
-        <v>272393.01</v>
-      </c>
-      <c r="W68" s="32" t="n">
-        <f aca="false">SUM(W7,W8,W9,W10,W11,W12,W13,W14,W15,W16,W17,W21,W22,W23,W27,W28,W32,W33,W34,W35,W39,W40,W41,W42,W46,W50,W51,W52,W53,W54,W55,W56,W60,W61,W62,W63,W64,W65)</f>
-        <v>263612.35</v>
+      <c r="H72" s="32" t="n">
+        <f aca="false">H21+H27+H32+H39+H46+H50+H60+H70</f>
+        <v>486155.016666667</v>
+      </c>
+      <c r="I72" s="32" t="n">
+        <f aca="false">I21+I27+I32+I39+I46+I50+I60+I70</f>
+        <v>194462.006666667</v>
+      </c>
+      <c r="J72" s="32" t="n">
+        <f aca="false">J21+J27+J32+J39+J46+J50+J60+J70</f>
+        <v>291693.01</v>
+      </c>
+      <c r="W72" s="32" t="n">
+        <f aca="false">SUM(W7,W8,W9,W10,W11,W12,W13,W14,W15,W16,W17,W18,W19,W20,W24,W25,W26,W30,W31,W35,W36,W37,W38,W42,W43,W44,W45,W49,W53,W54,W55,W56,W57,W58,W59,W63,W64,W65,W66,W67,W68,W69)</f>
+        <v>282912.35</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A3:V3"/>
   </mergeCells>
-  <conditionalFormatting sqref="X6:X68">
+  <conditionalFormatting sqref="X6:X72">
     <cfRule type="cellIs" priority="2" operator="greaterThan" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>0</formula>
     </cfRule>
@@ -5198,35 +5609,35 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="34" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>198</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="35" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="D4" s="35" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="E4" s="35" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F4" s="35" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G4" s="35" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5234,7 +5645,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="C5" s="30" t="n">
         <v>8</v>
@@ -5243,14 +5654,14 @@
         <v>1100</v>
       </c>
       <c r="E5" s="22" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F5" s="14" t="n">
         <f aca="false">C5*D5</f>
         <v>8800</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5258,7 +5669,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>1500</v>
@@ -5267,14 +5678,14 @@
         <v>1</v>
       </c>
       <c r="E6" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F6" s="14" t="n">
         <f aca="false">C6*D6</f>
         <v>1500</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5282,7 +5693,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>6000</v>
@@ -5291,14 +5702,14 @@
         <v>1</v>
       </c>
       <c r="E7" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F7" s="14" t="n">
         <f aca="false">C7*D7</f>
         <v>6000</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5306,7 +5717,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>7500</v>
@@ -5315,14 +5726,14 @@
         <v>1</v>
       </c>
       <c r="E8" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F8" s="14" t="n">
         <f aca="false">C8*D8</f>
         <v>7500</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5330,7 +5741,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="C9" s="30" t="n">
         <v>6.5</v>
@@ -5339,14 +5750,14 @@
         <v>900</v>
       </c>
       <c r="E9" s="22" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F9" s="14" t="n">
         <f aca="false">C9*D9</f>
         <v>5850</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5354,7 +5765,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>214</v>
+        <v>231</v>
       </c>
       <c r="C10" s="30" t="n">
         <v>14</v>
@@ -5363,14 +5774,14 @@
         <v>700</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F10" s="14" t="n">
         <f aca="false">C10*D10</f>
         <v>9800</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5378,7 +5789,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>216</v>
+        <v>233</v>
       </c>
       <c r="C11" s="30" t="n">
         <v>1.5</v>
@@ -5387,14 +5798,14 @@
         <v>700</v>
       </c>
       <c r="E11" s="22" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F11" s="14" t="n">
         <f aca="false">C11*D11</f>
         <v>1050</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>217</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5402,7 +5813,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="23" t="s">
-        <v>218</v>
+        <v>235</v>
       </c>
       <c r="C12" s="30" t="n">
         <v>3.5</v>
@@ -5411,14 +5822,14 @@
         <v>500</v>
       </c>
       <c r="E12" s="22" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
       <c r="F12" s="14" t="n">
         <f aca="false">C12*D12</f>
         <v>1750</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>220</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5426,7 +5837,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="23" t="s">
-        <v>221</v>
+        <v>238</v>
       </c>
       <c r="C13" s="30" t="n">
         <v>85</v>
@@ -5435,14 +5846,14 @@
         <v>40</v>
       </c>
       <c r="E13" s="22" t="s">
-        <v>222</v>
+        <v>239</v>
       </c>
       <c r="F13" s="14" t="n">
         <f aca="false">C13*D13</f>
         <v>3400</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>223</v>
+        <v>240</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5450,7 +5861,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="23" t="s">
-        <v>224</v>
+        <v>241</v>
       </c>
       <c r="C14" s="10" t="n">
         <v>2000</v>
@@ -5459,14 +5870,14 @@
         <v>1</v>
       </c>
       <c r="E14" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F14" s="14" t="n">
         <f aca="false">C14*D14</f>
         <v>2000</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5474,7 +5885,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="23" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="C15" s="30" t="n">
         <v>16.67</v>
@@ -5483,14 +5894,14 @@
         <v>270</v>
       </c>
       <c r="E15" s="22" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F15" s="14" t="n">
         <f aca="false">C15*D15</f>
         <v>4500.9</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5498,7 +5909,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="23" t="s">
-        <v>227</v>
+        <v>244</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>800</v>
@@ -5507,14 +5918,14 @@
         <v>1</v>
       </c>
       <c r="E16" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F16" s="14" t="n">
         <f aca="false">C16*D16</f>
         <v>800</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5522,7 +5933,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="23" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>600</v>
@@ -5531,19 +5942,19 @@
         <v>1</v>
       </c>
       <c r="E17" s="22" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="F17" s="14" t="n">
         <f aca="false">C17*D17</f>
         <v>600</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>229</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>230</v>
+        <v>247</v>
       </c>
       <c r="F18" s="13" t="n">
         <f aca="false">SUM(F5:F17)</f>
@@ -5552,7 +5963,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="6" t="s">
-        <v>231</v>
+        <v>248</v>
       </c>
       <c r="F20" s="10" t="n">
         <v>78000</v>
@@ -5560,7 +5971,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="6" t="s">
-        <v>232</v>
+        <v>249</v>
       </c>
       <c r="F21" s="10" t="n">
         <v>109500</v>
@@ -5568,16 +5979,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="6" t="s">
-        <v>233</v>
+        <v>250</v>
       </c>
       <c r="F22" s="11" t="n">
-        <f aca="false">'Bid Leveling'!L46</f>
+        <f aca="false">'Bid Leveling'!L49</f>
         <v>37500</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="6" t="s">
-        <v>234</v>
+        <v>251</v>
       </c>
       <c r="F23" s="25" t="n">
         <f aca="false">F22-F18</f>
@@ -5612,24 +6023,24 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="34" t="s">
-        <v>235</v>
+        <v>252</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="36" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>236</v>
+        <v>253</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="D3" s="36" t="s">
-        <v>238</v>
+        <v>255</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5637,16 +6048,16 @@
         <v>1</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>239</v>
+        <v>256</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="D4" s="27" t="n">
         <v>15550</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>241</v>
+        <v>258</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5654,16 +6065,16 @@
         <v>2</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>242</v>
+        <v>259</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>243</v>
+        <v>260</v>
       </c>
       <c r="D5" s="27" t="n">
         <v>850</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>244</v>
+        <v>261</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5671,14 +6082,14 @@
         <v>3</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>245</v>
+        <v>262</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>246</v>
+        <v>263</v>
       </c>
       <c r="D6" s="27"/>
       <c r="E6" s="8" t="s">
-        <v>247</v>
+        <v>264</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5686,16 +6097,16 @@
         <v>4</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>248</v>
+        <v>265</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>750</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>249</v>
+        <v>266</v>
       </c>
     </row>
   </sheetData>
@@ -5714,7 +6125,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -5724,18 +6135,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="34" t="s">
-        <v>250</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="36" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>251</v>
+        <v>268</v>
       </c>
       <c r="C3" s="36" t="s">
-        <v>252</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5743,10 +6154,10 @@
         <v>1</v>
       </c>
       <c r="B4" s="37" t="s">
-        <v>253</v>
+        <v>270</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>254</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5754,10 +6165,10 @@
         <v>2</v>
       </c>
       <c r="B5" s="37" t="s">
-        <v>255</v>
+        <v>272</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5765,10 +6176,10 @@
         <v>3</v>
       </c>
       <c r="B6" s="37" t="s">
-        <v>257</v>
+        <v>274</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>258</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5776,10 +6187,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="37" t="s">
-        <v>259</v>
+        <v>276</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>260</v>
+        <v>277</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5787,10 +6198,10 @@
         <v>5</v>
       </c>
       <c r="B8" s="37" t="s">
-        <v>261</v>
+        <v>278</v>
       </c>
       <c r="C8" s="23" t="s">
-        <v>262</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5798,10 +6209,10 @@
         <v>6</v>
       </c>
       <c r="B9" s="37" t="s">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="C9" s="23" t="s">
-        <v>264</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5809,10 +6220,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="37" t="s">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="C10" s="23" t="s">
-        <v>266</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5820,10 +6231,10 @@
         <v>8</v>
       </c>
       <c r="B11" s="37" t="s">
-        <v>267</v>
+        <v>284</v>
       </c>
       <c r="C11" s="23" t="s">
-        <v>268</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5831,10 +6242,10 @@
         <v>9</v>
       </c>
       <c r="B12" s="37" t="s">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="C12" s="23" t="s">
-        <v>270</v>
+        <v>287</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5842,10 +6253,10 @@
         <v>10</v>
       </c>
       <c r="B13" s="37" t="s">
-        <v>271</v>
+        <v>288</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>272</v>
+        <v>289</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5853,10 +6264,10 @@
         <v>11</v>
       </c>
       <c r="B14" s="37" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="C14" s="23" t="s">
-        <v>274</v>
+        <v>291</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5864,10 +6275,65 @@
         <v>12</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="C15" s="23" t="s">
-        <v>276</v>
+        <v>293</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>296</v>
+      </c>
+      <c r="C17" s="23" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>298</v>
+      </c>
+      <c r="C18" s="23" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>300</v>
+      </c>
+      <c r="C19" s="23" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>302</v>
+      </c>
+      <c r="C20" s="23" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>
